--- a/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
+++ b/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
@@ -7,25 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALISANLAR" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROL" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALISANLAR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="Aksiyon1" hidden="0" function="0" vbProcedure="0">KARAR!$A$15</definedName>
@@ -119,8 +118,7 @@
     <definedName name="VeriKaliteSkoru" hidden="0" function="0" vbProcedure="0">KONTROL!$B$21</definedName>
     <definedName name="VeriKaliteUyariCeza" hidden="0" function="0" vbProcedure="0">AYARLAR!$C$28</definedName>
     <definedName name="YillikIscilikYuku" hidden="0" function="0" vbProcedure="0">MOTOR!$B$17</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'PANO'!$A$1:$V$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'RAPOR'!$A$1:$V$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'RAPOR'!$A$1:$V$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -128,14 +126,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="85">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -489,8 +488,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -563,8 +744,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -586,6 +833,95 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -597,7 +933,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1080,6 +1416,163 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="74" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="73" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="73" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="74" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="73" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="73" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="75" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1281,1077 +1774,6 @@
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Kıdem / İhbar / İzin Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!C20</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 10.792.907</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <explosion val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="1"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="bestFit"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$B$20:$B$22</f>
-              <strCache>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>Kıdem</v>
-                </pt>
-                <pt idx="1">
-                  <v>İhbar</v>
-                </pt>
-                <pt idx="2">
-                  <v>İzin</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$C$21:$C$22</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>1298267</v>
-                </pt>
-                <pt idx="1">
-                  <v>264533</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Bütçe Kullanımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!C23</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 500.000</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$B$23:$B$24</f>
-              <strCache>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>Bütçe</v>
-                </pt>
-                <pt idx="1">
-                  <v>Maliyet</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$C$24</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>12355707</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="42431214"/>
-        <axId val="40406636"/>
-      </barChart>
-      <catAx>
-        <axId val="42431214"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="40406636"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="40406636"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="42431214"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Bütçe Kullanımı ve Kalan Kapasite</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!C26</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>2471,1%</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$B$26:$B$27</f>
-              <strCache>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>Kullanım</v>
-                </pt>
-                <pt idx="1">
-                  <v>Kalan Kapasite</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$C$27</f>
-              <numCache>
-                <formatCode>0.0%;[RED]\(0.0%\);\-</formatCode>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="18668255"/>
-        <axId val="65510800"/>
-      </barChart>
-      <catAx>
-        <axId val="18668255"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="65510800"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="65510800"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="0.0%;[RED]\(0.0%\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="18668255"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Sonraki Çalışan Tahmini (aralık)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!C30</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 860.208</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$B$30:$B$32</f>
-              <strCache>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>Alt Bant</v>
-                </pt>
-                <pt idx="1">
-                  <v>Orta (Tahmin)</v>
-                </pt>
-                <pt idx="2">
-                  <v>Üst Bant</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$C$31:$C$32</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>955786.497064579</v>
-                </pt>
-                <pt idx="1">
-                  <v>1051365.14677104</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="44410427"/>
-        <axId val="31980973"/>
-      </barChart>
-      <catAx>
-        <axId val="44410427"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="31980973"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="31980973"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="44410427"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
               <a:t>Senaryo Toplam Maliyetleri</a:t>
             </a:r>
           </a:p>
@@ -2410,7 +1832,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2494,7 +1916,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2550,7 +1972,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2583,7 +2005,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2606,7 +2028,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2687,7 +2109,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2765,7 +2187,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2821,7 +2243,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2854,7 +2276,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2877,7 +2299,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2967,7 +2389,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -3059,7 +2481,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3115,7 +2537,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3148,7 +2570,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -4120,119 +3542,6 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>10</col>
-      <colOff>290160</colOff>
-      <row>34</row>
-      <rowOff>21600</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>11</col>
-      <colOff>398880</colOff>
-      <row>37</row>
-      <rowOff>21960</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>11</col>
-      <colOff>398880</colOff>
-      <row>40</row>
-      <rowOff>21600</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>11</col>
-      <colOff>398880</colOff>
-      <row>44</row>
-      <rowOff>21960</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
       <col>8</col>
       <colOff>0</colOff>
       <row>4</row>
@@ -4533,683 +3842,581 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="74" min="1" max="1"/>
-    <col width="16" customWidth="1" style="74" min="2" max="2"/>
-    <col width="20" customWidth="1" style="74" min="3" max="3"/>
-    <col width="20" customWidth="1" style="74" min="4" max="4"/>
-    <col width="20" customWidth="1" style="74" min="5" max="5"/>
-    <col width="14" customWidth="1" style="74" min="6" max="6"/>
-    <col width="22" customWidth="1" style="74" min="7" max="7"/>
-    <col width="14" customWidth="1" style="74" min="8" max="8"/>
-    <col width="16" customWidth="1" style="74" min="9" max="9"/>
+    <col width="3" customWidth="1" style="74" min="1" max="1"/>
+    <col width="18" customWidth="1" style="74" min="2" max="2"/>
+    <col width="15" customWidth="1" style="74" min="3" max="3"/>
+    <col width="12" customWidth="1" style="74" min="4" max="4"/>
+    <col width="16" customWidth="1" style="74" min="5" max="5"/>
+    <col width="18" customWidth="1" style="74" min="6" max="6"/>
+    <col width="6" customWidth="1" style="74" min="7" max="7"/>
+    <col width="24" customWidth="1" style="74" min="8" max="8"/>
+    <col width="15" customWidth="1" style="74" min="9" max="9"/>
+    <col width="14" customWidth="1" style="74" min="10" max="10"/>
+    <col width="12" customWidth="1" style="74" min="11" max="11"/>
+    <col width="18" customWidth="1" style="74" min="12" max="12"/>
+    <col width="18" customWidth="1" style="74" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="75" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — KIDEM IHBAR YUKU VE PERSONEL CIKARMA MALIYETI HESAPLAYICI YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="76" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="166" t="inlineStr">
+        <is>
+          <t>KIDEM IHBAR YUKU VE PERSONEL CIKARMA MALIYETI HESAPLAYICI — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="167" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="168" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="169" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="170" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="171" t="n"/>
+      <c r="D5" s="172" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="173" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="171" t="n"/>
+      <c r="G5" s="174" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="170" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="171" t="n"/>
+      <c r="J5" s="175" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="176" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="171" t="n"/>
+      <c r="M5" s="172" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="77" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="77" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="77" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="78" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="177" t="n"/>
+      <c r="C6" s="171" t="n"/>
+      <c r="D6" s="171" t="n"/>
+      <c r="E6" s="178" t="n"/>
+      <c r="F6" s="171" t="n"/>
+      <c r="G6" s="171" t="n"/>
+      <c r="H6" s="177" t="n"/>
+      <c r="I6" s="171" t="n"/>
+      <c r="J6" s="171" t="n"/>
+      <c r="K6" s="179" t="n"/>
+      <c r="L6" s="171" t="n"/>
+      <c r="M6" s="171" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="79" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="79" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="80" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="81" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="180" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="171" t="n"/>
+      <c r="D7" s="171" t="n"/>
+      <c r="E7" s="181" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="171" t="n"/>
+      <c r="G7" s="171" t="n"/>
+      <c r="H7" s="180" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="171" t="n"/>
+      <c r="J7" s="171" t="n"/>
+      <c r="K7" s="182" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="171" t="n"/>
+      <c r="M7" s="171" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="177" t="n"/>
+      <c r="C8" s="171" t="n"/>
+      <c r="D8" s="171" t="n"/>
+      <c r="E8" s="178" t="n"/>
+      <c r="F8" s="171" t="n"/>
+      <c r="G8" s="171" t="n"/>
+      <c r="H8" s="177" t="n"/>
+      <c r="I8" s="171" t="n"/>
+      <c r="J8" s="171" t="n"/>
+      <c r="K8" s="179" t="n"/>
+      <c r="L8" s="171" t="n"/>
+      <c r="M8" s="171" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="82" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="83" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="84" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="183" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="171" t="n"/>
+      <c r="D9" s="171" t="n"/>
+      <c r="E9" s="184" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="171" t="n"/>
+      <c r="G9" s="171" t="n"/>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="171" t="n"/>
+      <c r="J9" s="171" t="n"/>
+      <c r="K9" s="185" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="171" t="n"/>
+      <c r="M9" s="171" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="98" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="186" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="98" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="85" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="86" t="inlineStr">
+      <c r="B12" s="97" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="97" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="187" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="86" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="86" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="86" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="86" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="86" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="86" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="86" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="87" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="88" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="88" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="89">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="90">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="88" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="91" t="n">
+      <c r="C14" s="187" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="187" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="187" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="188" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="188" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="188" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="188" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="188" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="97" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="97" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="97" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="97" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="189" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="189" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="190" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="191" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="175" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="97" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="97" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="97" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="97" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="189" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="189" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="190" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="191" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="172" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="97" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="97" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="97" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="97" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="189" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="189" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="190" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="191" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="192" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="97" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="97" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="97" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="97" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="189" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="189" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="190" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="191" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="175" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="97" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="97" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="97" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="97" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="193" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="194" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="195" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="196" t="inlineStr"/>
+      <c r="L19" s="197" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="97" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="97" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="92" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="87" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="88" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="88" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="89">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="90">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="88" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="91" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="92" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="87" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="88" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="88" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="89">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="90">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="88" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="91" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="92" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="87" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="88" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="88" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="89">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="90">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="88" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="91" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="92" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="87" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="88" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="88" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="89">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="90">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="88" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="91" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="92" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="87" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="88" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="88" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="89">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="90">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="88" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="91" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="92" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="97" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="97" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="198" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="198" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="199" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="200" t="n"/>
+      <c r="M22" s="200" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="82" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="97" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="201" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="202" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="200" t="n"/>
+      <c r="M23" s="200" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="83" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="97" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="201" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="203" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="204" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="82" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="205" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="206" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="207" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AD32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="40" customWidth="1" style="100" min="1" max="1"/>
-    <col width="22" customWidth="1" style="100" min="2" max="2"/>
-    <col width="18" customWidth="1" style="100" min="3" max="3"/>
-    <col width="6" customWidth="1" style="100" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
-        <is>
-          <t>PANO — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" s="74">
-      <c r="A3" s="143" t="inlineStr">
-        <is>
-          <t>Yönetici Özeti</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="74">
-      <c r="A5" s="144" t="inlineStr">
-        <is>
-          <t>TOPLAM ÇIKARMA MALİYETİ</t>
-        </is>
-      </c>
-      <c r="D5" s="145" t="inlineStr">
-        <is>
-          <t>BÜTÇE KULLANIM ORANI</t>
-        </is>
-      </c>
-      <c r="G5" s="146" t="inlineStr">
-        <is>
-          <t>ORTALAMA KIDEM YILI</t>
-        </is>
-      </c>
-      <c r="J5" s="147" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" s="74">
-      <c r="A6" s="148">
-        <f>ToplamCikarmaMaliyeti</f>
-        <v/>
-      </c>
-      <c r="D6" s="149">
-        <f>ButceKullanimOrani</f>
-        <v/>
-      </c>
-      <c r="G6" s="150">
-        <f>OrtalamaKidemYil</f>
-        <v/>
-      </c>
-      <c r="J6" s="151">
-        <f>KararSonuc</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="74">
-      <c r="A8" s="130" t="inlineStr">
-        <is>
-          <t>Toplam Kıdem Tazminatı</t>
-        </is>
-      </c>
-      <c r="B8" s="129">
-        <f>ToplamKidem</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="74">
-      <c r="A9" s="130" t="inlineStr">
-        <is>
-          <t>Toplam İhbar Tazminatı</t>
-        </is>
-      </c>
-      <c r="B9" s="129">
-        <f>ToplamIhbar</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="74">
-      <c r="A10" s="130" t="inlineStr">
-        <is>
-          <t>Toplam İzin Ücreti</t>
-        </is>
-      </c>
-      <c r="B10" s="129">
-        <f>ToplamIzinUcreti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="74">
-      <c r="A11" s="130" t="inlineStr">
-        <is>
-          <t>Toplam Çalışan</t>
-        </is>
-      </c>
-      <c r="B11" s="128">
-        <f>ToplamCalisanSayisi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="74">
-      <c r="A12" s="130" t="inlineStr">
-        <is>
-          <t>Anomali Çalışan Adedi</t>
-        </is>
-      </c>
-      <c r="B12" s="128">
-        <f>AnomaliCalisanAdedi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="74">
-      <c r="A13" s="130" t="inlineStr">
-        <is>
-          <t>Veri Kalite Skoru</t>
-        </is>
-      </c>
-      <c r="B13" s="128">
-        <f>VeriKaliteSkoru</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="74">
-      <c r="A15" s="135" t="inlineStr">
-        <is>
-          <t>EN KRİTİK 3 İÇGÖRÜ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="74">
-      <c r="A16" s="142">
-        <f>"Toplam çıkarma maliyeti "&amp;TEXT(ToplamCikarmaMaliyeti,"#,##0")&amp;" ₺; bütçe kullanımı %"&amp;TEXT(ButceKullanimOrani,"0.0%")&amp;"."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="74">
-      <c r="A17" s="142">
-        <f>"Kıdem "&amp;TEXT(ToplamKidem,"#,##0")&amp;", ihbar "&amp;TEXT(ToplamIhbar,"#,##0")&amp;", izin "&amp;TEXT(ToplamIzinUcreti,"#,##0")&amp;" ₺."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="74">
-      <c r="A18" s="142">
-        <f>"Ortalama kıdem "&amp;TEXT(OrtalamaKidemYil,"0")&amp;" yıl; "&amp;AnomaliCalisanAdedi&amp;" çalışanda ücret anomalisi var."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="74">
-      <c r="A20" s="130" t="inlineStr">
-        <is>
-          <t>Maliyet Dağılımı</t>
-        </is>
-      </c>
-      <c r="B20" s="100" t="inlineStr">
-        <is>
-          <t>Kıdem</t>
-        </is>
-      </c>
-      <c r="C20" s="124">
-        <f>ToplamKidem</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="74">
-      <c r="B21" s="100" t="inlineStr">
-        <is>
-          <t>İhbar</t>
-        </is>
-      </c>
-      <c r="C21" s="124">
-        <f>ToplamIhbar</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="74">
-      <c r="B22" s="100" t="inlineStr">
-        <is>
-          <t>İzin</t>
-        </is>
-      </c>
-      <c r="C22" s="124">
-        <f>ToplamIzinUcreti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="74">
-      <c r="A23" s="130" t="inlineStr">
-        <is>
-          <t>Bütçe vs Maliyet</t>
-        </is>
-      </c>
-      <c r="B23" s="100" t="inlineStr">
-        <is>
-          <t>Bütçe</t>
-        </is>
-      </c>
-      <c r="C23" s="124">
-        <f>IFERROR(ButceFarki+ToplamCikarmaMaliyeti,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="74">
-      <c r="B24" s="100" t="inlineStr">
-        <is>
-          <t>Maliyet</t>
-        </is>
-      </c>
-      <c r="C24" s="124">
-        <f>ToplamCikarmaMaliyeti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="74">
-      <c r="A26" s="130" t="inlineStr">
-        <is>
-          <t>Bütçe Kullanım ve Kalan Kapasite</t>
-        </is>
-      </c>
-      <c r="B26" s="100" t="inlineStr">
-        <is>
-          <t>Kullanım</t>
-        </is>
-      </c>
-      <c r="C26" s="152">
-        <f>ButceKullanimOrani</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="74">
-      <c r="B27" s="100" t="inlineStr">
-        <is>
-          <t>Kalan Kapasite</t>
-        </is>
-      </c>
-      <c r="C27" s="152">
-        <f>MAX(0,1-ButceKullanimOrani)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="74">
-      <c r="A30" s="130" t="inlineStr">
-        <is>
-          <t>Tahmin Aralığı</t>
-        </is>
-      </c>
-      <c r="B30" s="100" t="inlineStr">
-        <is>
-          <t>Alt Bant</t>
-        </is>
-      </c>
-      <c r="C30" s="124">
-        <f>MAX(0,modulI1TahminOrta*(1-TahminBantOrani))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="74">
-      <c r="B31" s="100" t="inlineStr">
-        <is>
-          <t>Orta (Tahmin)</t>
-        </is>
-      </c>
-      <c r="C31" s="124">
-        <f>modulI1TahminOrta</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="74">
-      <c r="B32" s="100" t="inlineStr">
-        <is>
-          <t>Üst Bant</t>
-        </is>
-      </c>
-      <c r="C32" s="124">
-        <f>modulI1TahminOrta*(1+TahminBantOrani)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="12">
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0">
-    <oddHeader/>
-    <oddFooter>&amp;LKIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5574,7 +4781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5824,7 +5031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5984,7 +5191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6092,7 +5299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6201,7 +5408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6283,7 +5490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6354,7 +5561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7668,7 +6875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7815,241 +7022,473 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="B3:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="74" min="1" max="1"/>
-    <col width="30" customWidth="1" style="74" min="2" max="2"/>
-    <col width="18" customWidth="1" style="74" min="3" max="3"/>
-    <col width="10" customWidth="1" style="74" min="4" max="4"/>
-    <col width="12" customWidth="1" style="74" min="5" max="5"/>
+    <col width="3" customWidth="1" style="74" min="1" max="1"/>
+    <col width="14" customWidth="1" style="74" min="2" max="2"/>
+    <col width="16" customWidth="1" style="74" min="3" max="3"/>
+    <col width="32" customWidth="1" style="74" min="4" max="4"/>
+    <col width="18" customWidth="1" style="74" min="5" max="5"/>
     <col width="12" customWidth="1" style="74" min="6" max="6"/>
-    <col width="35" customWidth="1" style="74" min="7" max="7"/>
+    <col width="18" customWidth="1" style="74" min="7" max="7"/>
+    <col width="22" customWidth="1" style="74" min="8" max="8"/>
+    <col width="16" customWidth="1" style="74" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="93" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" s="208" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="209" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="210" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="B5" s="94" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="94" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="94" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="94" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="94" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="94" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
+      <c r="B5" s="211" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="211" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="211" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="211" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="211" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="211" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="211" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="211" t="inlineStr">
+        <is>
+          <t>DURUM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="96" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="87" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="97" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
+      <c r="B6" s="212" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="213" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="214" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="215" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="216" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="217">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="214" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="218" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="95" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="96" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="87" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="97" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
+      <c r="B7" s="219" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="220" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="221" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="222" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="223" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="224">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="221" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="225" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="95" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="96" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="87" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="97" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
+      <c r="B8" s="212" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="213" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="214" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="215" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="216" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="217">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="214" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="218" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="95" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="96" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="87" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="97" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
+      <c r="B9" s="219" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="220" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="221" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="222" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="223" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="224">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="221" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="226" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="96" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="87" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="97" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
+      <c r="B10" s="212" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="213" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="214" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="215" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="216" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="217">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="214" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="218" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="95" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="96" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="87" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="97" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
+      <c r="B11" s="219" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="220" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="221" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="222" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="223" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="224">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="221" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="227" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="212" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="213" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="214" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="215" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="216" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="217">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="214" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="218" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="219" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="220" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="221" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="222" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="223" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="224">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="221" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="226" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="212" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="213" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="214" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="215" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="216" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="217">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="214" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="218" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="219" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="220" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="221" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="222" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="223" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="224">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="221" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="226" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="228" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="196" t="n"/>
+      <c r="D17" s="196" t="n"/>
+      <c r="E17" s="229">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="196" t="n"/>
+      <c r="G17" s="196" t="n"/>
+      <c r="H17" s="196" t="n"/>
+      <c r="I17" s="196" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8061,81 +7500,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="74" min="1" max="1"/>
-    <col width="25" customWidth="1" style="74" min="2" max="2"/>
-    <col width="20" customWidth="1" style="74" min="3" max="3"/>
-    <col width="20" customWidth="1" style="74" min="4" max="4"/>
-    <col width="15" customWidth="1" style="74" min="5" max="5"/>
-    <col width="25" customWidth="1" style="74" min="6" max="6"/>
-    <col width="15" customWidth="1" style="74" min="7" max="7"/>
-    <col width="15" customWidth="1" style="74" min="8" max="8"/>
+    <col width="3" customWidth="1" style="74" min="1" max="1"/>
+    <col width="24" customWidth="1" style="74" min="2" max="2"/>
+    <col width="15" customWidth="1" style="74" min="3" max="3"/>
+    <col width="15" customWidth="1" style="74" min="4" max="4"/>
+    <col width="22" customWidth="1" style="74" min="5" max="5"/>
+    <col width="6" customWidth="1" style="74" min="6" max="6"/>
+    <col width="6" customWidth="1" style="74" min="7" max="7"/>
+    <col width="24" customWidth="1" style="74" min="8" max="8"/>
+    <col width="15" customWidth="1" style="74" min="9" max="9"/>
+    <col width="15" customWidth="1" style="74" min="10" max="10"/>
+    <col width="22" customWidth="1" style="74" min="11" max="11"/>
+    <col width="6" customWidth="1" style="74" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="93" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="98" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="230" t="inlineStr">
+        <is>
+          <t>KIDEM IHBAR YUKU VE PERSONEL CIKARMA MALIYETI HESAPLAYICI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="231" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="232" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="99" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="233" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="171" t="n"/>
+      <c r="D6" s="171" t="n"/>
+      <c r="E6" s="171" t="n"/>
+      <c r="F6" s="171" t="n"/>
+      <c r="H6" s="234" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="171" t="n"/>
+      <c r="J6" s="171" t="n"/>
+      <c r="K6" s="171" t="n"/>
+      <c r="L6" s="171" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="171" t="n"/>
+      <c r="C7" s="171" t="n"/>
+      <c r="D7" s="171" t="n"/>
+      <c r="E7" s="171" t="n"/>
+      <c r="F7" s="171" t="n"/>
+      <c r="H7" s="171" t="n"/>
+      <c r="I7" s="171" t="n"/>
+      <c r="J7" s="171" t="n"/>
+      <c r="K7" s="171" t="n"/>
+      <c r="L7" s="171" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="235" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="171" t="n"/>
+      <c r="D8" s="171" t="n"/>
+      <c r="E8" s="236" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="171" t="n"/>
+      <c r="H8" s="235" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="171" t="n"/>
+      <c r="J8" s="171" t="n"/>
+      <c r="K8" s="237" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="171" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="98" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="235" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="171" t="n"/>
+      <c r="D9" s="171" t="n"/>
+      <c r="E9" s="238" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="171" t="n"/>
+      <c r="H9" s="235" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="171" t="n"/>
+      <c r="J9" s="171" t="n"/>
+      <c r="K9" s="238" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="171" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="99" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="235" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="171" t="n"/>
+      <c r="D10" s="171" t="n"/>
+      <c r="E10" s="239" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="171" t="n"/>
+      <c r="H10" s="235" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="171" t="n"/>
+      <c r="J10" s="171" t="n"/>
+      <c r="K10" s="239" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="171" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="235" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="171" t="n"/>
+      <c r="D11" s="171" t="n"/>
+      <c r="E11" s="239" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="171" t="n"/>
+      <c r="H11" s="235" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="171" t="n"/>
+      <c r="J11" s="171" t="n"/>
+      <c r="K11" s="239" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="171" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="171" t="n"/>
+      <c r="C12" s="171" t="n"/>
+      <c r="D12" s="171" t="n"/>
+      <c r="E12" s="171" t="n"/>
+      <c r="F12" s="171" t="n"/>
+      <c r="H12" s="171" t="n"/>
+      <c r="I12" s="171" t="n"/>
+      <c r="J12" s="171" t="n"/>
+      <c r="K12" s="171" t="n"/>
+      <c r="L12" s="171" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="98" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="171" t="n"/>
+      <c r="C13" s="171" t="n"/>
+      <c r="D13" s="171" t="n"/>
+      <c r="E13" s="171" t="n"/>
+      <c r="F13" s="171" t="n"/>
+      <c r="H13" s="171" t="n"/>
+      <c r="I13" s="171" t="n"/>
+      <c r="J13" s="171" t="n"/>
+      <c r="K13" s="171" t="n"/>
+      <c r="L13" s="171" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="240" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="171" t="n"/>
+      <c r="D14" s="171" t="n"/>
+      <c r="E14" s="171" t="n"/>
+      <c r="F14" s="171" t="n"/>
+      <c r="H14" s="241" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="171" t="n"/>
+      <c r="J14" s="171" t="n"/>
+      <c r="K14" s="171" t="n"/>
+      <c r="L14" s="171" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="95" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="95" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="171" t="n"/>
+      <c r="C15" s="171" t="n"/>
+      <c r="D15" s="171" t="n"/>
+      <c r="E15" s="171" t="n"/>
+      <c r="F15" s="171" t="n"/>
+      <c r="H15" s="171" t="n"/>
+      <c r="I15" s="171" t="n"/>
+      <c r="J15" s="171" t="n"/>
+      <c r="K15" s="171" t="n"/>
+      <c r="L15" s="171" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="85" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="198" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="198" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="198" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="198" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
+++ b/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
@@ -132,13 +132,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="99">
     <font>
@@ -1336,7 +1337,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2047,6 +2048,24 @@
     </xf>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="58" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="61" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="62" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="65" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="66" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="84" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="54" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -41703,7 +41722,7 @@
     <col width="6" customWidth="1" style="74" min="7" max="7"/>
     <col width="24" customWidth="1" style="74" min="8" max="8"/>
     <col width="15" customWidth="1" style="74" min="9" max="9"/>
-    <col width="14" customWidth="1" style="74" min="10" max="10"/>
+    <col width="15" customWidth="1" style="74" min="10" max="10"/>
     <col width="12" customWidth="1" style="74" min="11" max="11"/>
     <col width="18" customWidth="1" style="74" min="12" max="12"/>
     <col width="18" customWidth="1" style="74" min="13" max="13"/>
@@ -41719,7 +41738,7 @@
     <row r="2">
       <c r="B2" s="166" t="inlineStr">
         <is>
-          <t>KIDEM IHBAR YUKU VE PERSONEL CIKARMA MALIYETI HESAPLAYICI — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI</t>
         </is>
       </c>
       <c r="L2" s="167" t="inlineStr">
@@ -41736,7 +41755,7 @@
     <row r="3">
       <c r="B3" s="169" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: İnsan kaynakları yöneticileri, işverenler, mali müşavirler ve personel çıkarma planı yapan işletme sahipleri · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
@@ -41749,23 +41768,23 @@
       <c r="C5" s="171" t="n"/>
       <c r="D5" s="172" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="173" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>OPERASYONEL MALİYET</t>
         </is>
       </c>
       <c r="F5" s="171" t="n"/>
       <c r="G5" s="174" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="170" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="171" t="n"/>
@@ -41801,31 +41820,27 @@
       <c r="M6" s="171" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="180" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="267">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="171" t="n"/>
       <c r="D7" s="171" t="n"/>
-      <c r="E7" s="181" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="268">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="171" t="n"/>
       <c r="G7" s="171" t="n"/>
-      <c r="H7" s="180" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="267">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="171" t="n"/>
       <c r="J7" s="171" t="n"/>
-      <c r="K7" s="182" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="182">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="171" t="n"/>
       <c r="M7" s="171" t="n"/>
@@ -41847,28 +41862,28 @@
     <row r="9">
       <c r="B9" s="183" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="171" t="n"/>
       <c r="D9" s="171" t="n"/>
       <c r="E9" s="184" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="171" t="n"/>
       <c r="G9" s="171" t="n"/>
       <c r="H9" s="183" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="171" t="n"/>
       <c r="J9" s="171" t="n"/>
       <c r="K9" s="185" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="171" t="n"/>
@@ -41877,7 +41892,7 @@
     <row r="11">
       <c r="B11" s="98" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="186" t="inlineStr">
@@ -41894,7 +41909,7 @@
     <row r="12">
       <c r="B12" s="97" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="97" t="inlineStr">
@@ -41967,18 +41982,16 @@
       </c>
       <c r="H15" s="189" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="189" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="190" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="269">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="270">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="191" t="inlineStr">
         <is>
@@ -42008,18 +42021,16 @@
       </c>
       <c r="H16" s="189" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="189" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="190" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="269">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="270">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="191" t="inlineStr">
         <is>
@@ -42049,18 +42060,16 @@
       </c>
       <c r="H17" s="189" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="189" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="190" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="269">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="270">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="191" t="inlineStr">
         <is>
@@ -42090,18 +42099,16 @@
       </c>
       <c r="H18" s="189" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="189" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="190" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="269">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="270">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="191" t="inlineStr">
         <is>
@@ -42134,15 +42141,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="194" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="195" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="271">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="272">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="196" t="inlineStr"/>
       <c r="L19" s="197" t="inlineStr">
@@ -42204,7 +42209,7 @@
       </c>
       <c r="K23" s="202" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="200" t="n"/>
@@ -42228,7 +42233,7 @@
       </c>
       <c r="K24" s="203" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -44020,7 +44025,7 @@
     <row r="3">
       <c r="B3" s="208" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="209" t="inlineStr">
@@ -44089,10 +44094,10 @@
       </c>
       <c r="D6" s="214" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="215" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="273" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="216" t="n">
@@ -44126,10 +44131,10 @@
       </c>
       <c r="D7" s="221" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="222" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="273" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="223" t="n">
@@ -44163,10 +44168,10 @@
       </c>
       <c r="D8" s="214" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="215" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="273" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="216" t="n">
@@ -44200,10 +44205,10 @@
       </c>
       <c r="D9" s="221" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="222" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="273" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="223" t="n">
@@ -44237,10 +44242,10 @@
       </c>
       <c r="D10" s="214" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="215" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="273" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="216" t="n">
@@ -44274,10 +44279,10 @@
       </c>
       <c r="D11" s="221" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="222" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="273" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="223" t="n">
@@ -44289,7 +44294,7 @@
       </c>
       <c r="H11" s="221" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="227" t="inlineStr">
@@ -44311,10 +44316,10 @@
       </c>
       <c r="D12" s="214" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="215" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="273" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="216" t="n">
@@ -44326,7 +44331,7 @@
       </c>
       <c r="H12" s="214" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="218" t="inlineStr">
@@ -44348,10 +44353,10 @@
       </c>
       <c r="D13" s="221" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="222" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="273" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="223" t="n">
@@ -44385,10 +44390,10 @@
       </c>
       <c r="D14" s="214" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="215" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="273" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="216" t="n">
@@ -44422,10 +44427,10 @@
       </c>
       <c r="D15" s="221" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="222" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="273" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="223" t="n">
@@ -44509,14 +44514,14 @@
     <row r="2">
       <c r="B2" s="230" t="inlineStr">
         <is>
-          <t>KIDEM IHBAR YUKU VE PERSONEL CIKARMA MALIYETI HESAPLAYICI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="231" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · İnsan kaynakları yöneticileri, işverenler, mali müşavirler ve personel çıkarma planı yapan işletme sahipleri</t>
         </is>
       </c>
     </row>
@@ -44595,10 +44600,9 @@
       </c>
       <c r="C9" s="171" t="n"/>
       <c r="D9" s="171" t="n"/>
-      <c r="E9" s="238" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="274">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="171" t="n"/>
       <c r="H9" s="235" t="inlineStr">
@@ -44608,10 +44612,9 @@
       </c>
       <c r="I9" s="171" t="n"/>
       <c r="J9" s="171" t="n"/>
-      <c r="K9" s="238" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="274">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="171" t="n"/>
     </row>
@@ -44623,10 +44626,9 @@
       </c>
       <c r="C10" s="171" t="n"/>
       <c r="D10" s="171" t="n"/>
-      <c r="E10" s="239" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="275">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="171" t="n"/>
       <c r="H10" s="235" t="inlineStr">
@@ -44636,10 +44638,9 @@
       </c>
       <c r="I10" s="171" t="n"/>
       <c r="J10" s="171" t="n"/>
-      <c r="K10" s="239" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="275">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="171" t="n"/>
     </row>
@@ -44651,10 +44652,9 @@
       </c>
       <c r="C11" s="171" t="n"/>
       <c r="D11" s="171" t="n"/>
-      <c r="E11" s="239" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="276">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="171" t="n"/>
       <c r="H11" s="235" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
+++ b/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
@@ -141,7 +141,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="99">
+  <fonts count="101">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -758,8 +758,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -961,6 +973,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1337,7 +1355,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2066,6 +2084,30 @@
     </xf>
     <xf numFmtId="170" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4337,20 +4379,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="74" min="1" max="1"/>
-    <col width="78" customWidth="1" style="74" min="2" max="2"/>
+    <col width="147.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="74">
-      <c r="A1" s="243" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="244" t="inlineStr">
         <is>
@@ -4615,6 +4674,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="74">
       <c r="A26" s="247" t="inlineStr">
         <is>
@@ -4713,7 +4773,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4729,17 +4789,35 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="60" customWidth="1" style="100" min="1" max="3"/>
+    <col width="13" customWidth="1" style="74" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1" s="74">
-      <c r="A1" s="101" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" s="74">
-      <c r="A3" s="102" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Personel çıkarma kararınızın maliyetini tam ve mevzuata uygun hesaplayın.</t>
         </is>
@@ -4774,6 +4852,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="74">
       <c r="A10" s="105" t="inlineStr">
         <is>
@@ -4784,6 +4863,7 @@
     <row r="11" ht="15" customHeight="1" s="74"/>
     <row r="12" ht="15" customHeight="1" s="74"/>
     <row r="13" ht="15" customHeight="1" s="74"/>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="74">
       <c r="A15" s="106" t="inlineStr">
         <is>
@@ -4804,11 +4884,11 @@
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A10:C13"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C5"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4825,8 +4905,16 @@
   <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="72" customWidth="1" style="100" min="1" max="1"/>
+    <col width="126.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="20" customWidth="1" style="100" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4836,8 +4924,9 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="74">
-      <c r="A3" s="108" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Nasıl kullanılır?</t>
         </is>
@@ -4892,6 +4981,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="74">
       <c r="A12" s="110" t="inlineStr">
         <is>
@@ -4934,6 +5024,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="74">
       <c r="A19" s="111" t="inlineStr">
         <is>
@@ -4943,7 +5034,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A8:AN8"/>
     <mergeCell ref="A6:AN6"/>
     <mergeCell ref="A4:AN4"/>
@@ -4953,6 +5044,7 @@
     <mergeCell ref="A19:AN19"/>
     <mergeCell ref="A10:AN10"/>
     <mergeCell ref="A5:AN5"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A13:AN13"/>
     <mergeCell ref="A14:AN14"/>
     <mergeCell ref="A17:AN17"/>
@@ -4974,31 +5066,51 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="100" min="1" max="1"/>
-    <col width="14" customWidth="1" style="100" min="2" max="4"/>
-    <col width="12" customWidth="1" style="100" min="5" max="5"/>
-    <col width="14" customWidth="1" style="100" min="6" max="6"/>
-    <col width="10" customWidth="1" style="100" min="7" max="8"/>
-    <col width="16" customWidth="1" style="100" min="9" max="9"/>
-    <col width="10" customWidth="1" style="100" min="10" max="10"/>
-    <col width="16" customWidth="1" style="100" min="11" max="11"/>
-    <col width="12" customWidth="1" style="100" min="12" max="13"/>
-    <col width="18" customWidth="1" style="100" min="14" max="14"/>
+    <col width="23.5" customWidth="1" style="100" min="2" max="4"/>
+    <col width="23.5" customWidth="1" style="74" min="3" max="3"/>
+    <col width="18.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="14.5" customWidth="1" style="100" min="5" max="5"/>
+    <col width="20.5" customWidth="1" style="100" min="6" max="6"/>
+    <col width="13.5" customWidth="1" style="100" min="7" max="8"/>
+    <col width="13.5" customWidth="1" style="74" min="8" max="8"/>
+    <col width="23.5" customWidth="1" style="100" min="9" max="9"/>
+    <col width="13.5" customWidth="1" style="100" min="10" max="10"/>
+    <col width="23.5" customWidth="1" style="100" min="11" max="11"/>
+    <col width="20.5" customWidth="1" style="100" min="12" max="13"/>
+    <col width="25.5" customWidth="1" style="74" min="13" max="13"/>
+    <col width="31.5" customWidth="1" style="100" min="14" max="14"/>
+    <col width="13" customWidth="1" style="74" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>CALISANLAR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+      <c r="J1" s="278" t="n"/>
+      <c r="K1" s="278" t="n"/>
+      <c r="L1" s="278" t="n"/>
+      <c r="M1" s="278" t="n"/>
+      <c r="N1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Çalışanlar, Kıdem ve Çıkarma Maliyeti</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="74">
       <c r="A5" s="114" t="inlineStr">
         <is>
@@ -21607,6 +21719,7 @@
       <c r="E1004" s="121" t="n"/>
       <c r="M1004" s="121" t="n"/>
     </row>
+    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="74">
       <c r="A1006" s="111" t="inlineStr">
         <is>
@@ -21619,7 +21732,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1006:AN1006"/>
     <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="I6">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
@@ -39628,22 +39741,43 @@
   <cols>
     <col width="56" customWidth="1" style="100" min="1" max="1"/>
     <col width="34" customWidth="1" style="100" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
+    <col width="13" customWidth="1" style="74" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>MOTOR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+      <c r="J1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Hesaplama Motoru — Kıdem, İhbar, İzin ve Maliyet</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="74">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -39820,6 +39954,9 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="74">
       <c r="A25" s="113" t="inlineStr">
         <is>
@@ -40014,6 +40151,7 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="74">
       <c r="A44" s="113" t="inlineStr">
         <is>
@@ -40246,6 +40384,7 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
     <row r="61" ht="19.5" customHeight="1" s="74">
       <c r="A61" s="111" t="inlineStr">
         <is>
@@ -40255,24 +40394,25 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="17">
-    <mergeCell ref="C48:Z48"/>
-    <mergeCell ref="A61:AN61"/>
+  <mergeCells count="18">
+    <mergeCell ref="C47:Z47"/>
+    <mergeCell ref="C54:Z54"/>
+    <mergeCell ref="C50:Z50"/>
+    <mergeCell ref="C55:Z55"/>
     <mergeCell ref="C56:Z56"/>
-    <mergeCell ref="C49:Z49"/>
     <mergeCell ref="C59:Z59"/>
     <mergeCell ref="C51:Z51"/>
     <mergeCell ref="C46:Z46"/>
-    <mergeCell ref="C47:Z47"/>
-    <mergeCell ref="C54:Z54"/>
+    <mergeCell ref="C52:Z52"/>
+    <mergeCell ref="C48:Z48"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C57:Z57"/>
+    <mergeCell ref="C53:Z53"/>
+    <mergeCell ref="A61:AN61"/>
+    <mergeCell ref="C49:Z49"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="C58:Z58"/>
-    <mergeCell ref="C50:Z50"/>
-    <mergeCell ref="C57:Z57"/>
-    <mergeCell ref="C55:Z55"/>
-    <mergeCell ref="C53:Z53"/>
     <mergeCell ref="C45:Z45"/>
-    <mergeCell ref="C52:Z52"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B10">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -40308,24 +40448,42 @@
   <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="46" customWidth="1" style="100" min="1" max="1"/>
+    <col width="63.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="14" customWidth="1" style="100" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>KONTROL — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Veri Kalitesi ve Sağlık Kontrolü</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -40333,6 +40491,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="74">
       <c r="A7" s="136" t="inlineStr">
         <is>
@@ -40443,6 +40602,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="74">
       <c r="A18" s="135" t="inlineStr">
         <is>
@@ -40494,6 +40654,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="74">
       <c r="A24" s="136" t="inlineStr">
         <is>
@@ -40505,6 +40666,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="19.5" customHeight="1" s="74">
       <c r="A26" s="111" t="inlineStr">
         <is>
@@ -40514,9 +40676,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A26:AN26"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -40660,18 +40823,34 @@
   <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="46" customWidth="1" style="100" min="1" max="1"/>
+    <col width="101.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="28" customWidth="1" style="100" min="2" max="2"/>
     <col width="22" customWidth="1" style="100" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>KARAR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="74">
       <c r="A3" s="113" t="inlineStr">
         <is>
@@ -40679,6 +40858,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -40730,6 +40910,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="18.75" customHeight="1" s="74">
       <c r="A11" s="113" t="inlineStr">
         <is>
@@ -40752,6 +40933,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="74">
       <c r="A14" s="135" t="inlineStr">
         <is>
@@ -40783,6 +40965,8 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="19.5" customHeight="1" s="74">
       <c r="A21" s="111" t="inlineStr">
         <is>
@@ -40796,9 +40980,9 @@
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B11">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -40829,26 +41013,42 @@
   <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="100" min="1" max="1"/>
+    <col width="61.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="16" customWidth="1" style="100" min="2" max="3"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
     <col width="18" customWidth="1" style="100" min="4" max="6"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
     <col width="14" customWidth="1" style="100" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>SENARYO DUYARLILIK — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Senaryo ve Duyarlılık Analizi</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -40986,6 +41186,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="74">
       <c r="A11" s="135" t="inlineStr">
         <is>
@@ -41092,6 +41293,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="74">
       <c r="A16" s="135" t="inlineStr">
         <is>
@@ -41132,6 +41334,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="19.5" customHeight="1" s="74">
       <c r="A21" s="111" t="inlineStr">
         <is>
@@ -41141,9 +41344,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A21:AN21"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="G7">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
@@ -41194,17 +41398,32 @@
   <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="46" customWidth="1" style="100" min="1" max="1"/>
+    <col width="146.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="26" customWidth="1" style="100" min="2" max="2"/>
     <col width="14" customWidth="1" style="100" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="154" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>KIDEM–İHBAR YÜKÜ VE ÇIKARMA MALİYETİ RAPORU</t>
         </is>
       </c>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="74">
       <c r="A2" s="104">
@@ -41212,12 +41431,13 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="107">
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296">
         <f>TEXT(raporTarihi,"gg.aa.yyyy") &amp; " | Rapor: " &amp; TEXT(raporTarihi,"gg.aa.yyyy")</f>
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -41280,6 +41500,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="74">
       <c r="A12" s="135" t="inlineStr">
         <is>
@@ -41293,6 +41514,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="74">
       <c r="A15" s="135" t="inlineStr">
         <is>
@@ -41335,6 +41557,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="74">
       <c r="A22" s="135" t="inlineStr">
         <is>
@@ -41354,6 +41577,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="74">
       <c r="A26" s="135" t="inlineStr">
         <is>
@@ -41379,6 +41603,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="74">
       <c r="A31" s="158">
         <f>firmaUnvani &amp; " | " &amp; TEXT(raporTarihi,"gg.aa.yyyy") &amp; " | Rev 1.0"</f>
@@ -41394,19 +41619,20 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:AN1"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
@@ -41446,18 +41672,34 @@
   <cols>
     <col width="24" customWidth="1" style="100" min="1" max="1"/>
     <col width="14" customWidth="1" style="100" min="2" max="4"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
     <col width="12" customWidth="1" style="100" min="5" max="6"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>ORNEK VERI — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Örnek Veri ve İçe Aktarma Yapısı</t>
         </is>
@@ -41470,6 +41712,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1" s="74">
       <c r="A6" s="114" t="inlineStr">
         <is>
@@ -41574,6 +41817,8 @@
         <v>2</v>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12" ht="19.5" customHeight="1" s="74">
       <c r="A12" s="111" t="inlineStr">
         <is>
@@ -41583,8 +41828,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="3">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A12:AN12"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -41601,16 +41847,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13" customWidth="1" style="74" min="1" max="1"/>
+    <col width="27.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="74">
-      <c r="A1" s="100" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>KURALLAR — eski35_kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici_uretildi</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="74">
       <c r="A3" s="100" t="inlineStr">
         <is>
@@ -41697,6 +41964,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -41710,22 +41980,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
-    <col width="18" customWidth="1" style="74" min="2" max="2"/>
+    <col width="92.5" customWidth="1" style="74" min="2" max="2"/>
     <col width="15" customWidth="1" style="74" min="3" max="3"/>
-    <col width="12" customWidth="1" style="74" min="4" max="4"/>
-    <col width="16" customWidth="1" style="74" min="5" max="5"/>
+    <col width="15.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="36.5" customWidth="1" style="74" min="5" max="5"/>
     <col width="18" customWidth="1" style="74" min="6" max="6"/>
-    <col width="6" customWidth="1" style="74" min="7" max="7"/>
-    <col width="24" customWidth="1" style="74" min="8" max="8"/>
+    <col width="11.5" customWidth="1" style="74" min="7" max="7"/>
+    <col width="75.5" customWidth="1" style="74" min="8" max="8"/>
     <col width="15" customWidth="1" style="74" min="9" max="9"/>
-    <col width="15" customWidth="1" style="74" min="10" max="10"/>
-    <col width="12" customWidth="1" style="74" min="11" max="11"/>
+    <col width="15.5" customWidth="1" style="74" min="10" max="10"/>
+    <col width="81.5" customWidth="1" style="74" min="11" max="11"/>
     <col width="18" customWidth="1" style="74" min="12" max="12"/>
     <col width="18" customWidth="1" style="74" min="13" max="13"/>
+    <col width="13" customWidth="1" style="74" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41759,6 +42030,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="170" t="inlineStr">
         <is>
@@ -41889,6 +42161,7 @@
       <c r="L9" s="171" t="n"/>
       <c r="M9" s="171" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="98" t="inlineStr">
         <is>
@@ -41918,6 +42191,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="187" t="inlineStr">
         <is>
@@ -42172,6 +42446,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="198" t="inlineStr">
         <is>
@@ -42260,13 +42535,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="279" t="n"/>
+      <c r="H26" s="279" t="n"/>
+      <c r="I26" s="280" t="n"/>
       <c r="K26" s="207" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="281" t="n"/>
+      <c r="G27" s="282" t="n"/>
+      <c r="H27" s="282" t="n"/>
+      <c r="I27" s="283" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -42283,23 +42566,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13" customWidth="1" style="74" min="1" max="1"/>
+    <col width="26.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="15.5" customWidth="1" style="74" min="3" max="3"/>
+    <col width="18.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="14.5" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="74">
-      <c r="A1" s="100" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>VAKALAR — eski35_kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici_uretildi</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="100" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Tebliğ tarzı altın vakalar</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="100" t="inlineStr">
         <is>
@@ -42380,6 +42683,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -42395,25 +42702,42 @@
   <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="14" customWidth="1" style="100" min="1" max="1"/>
+    <col width="61.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="10" customWidth="1" style="100" min="2" max="2"/>
-    <col width="80" customWidth="1" style="100" min="3" max="3"/>
+    <col width="135.5" customWidth="1" style="100" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>DEGISIKLIK KAYDI — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Değişiklik Kaydı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="74">
       <c r="A5" s="114" t="inlineStr">
         <is>
@@ -42448,6 +42772,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="19.5" customHeight="1" s="74">
       <c r="A8" s="111" t="inlineStr">
         <is>
@@ -42457,10 +42782,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A8:AN8"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -42482,17 +42808,31 @@
     <col width="30" customWidth="1" style="100" min="3" max="3"/>
     <col width="3" customWidth="1" style="100" min="4" max="4"/>
     <col width="30" customWidth="1" style="100" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>LISTELER — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Açılır Liste Kaynakları</t>
         </is>
@@ -42505,6 +42845,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="74">
       <c r="A6" s="115" t="inlineStr">
         <is>
@@ -42519,6 +42860,8 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10" ht="19.5" customHeight="1" s="74">
       <c r="A10" s="111" t="inlineStr">
         <is>
@@ -42528,9 +42871,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A10:AN10"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -42548,24 +42892,34 @@
   <dimension ref="A1:AN39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="100" min="1" max="1"/>
+    <col width="78.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="26" customWidth="1" style="100" min="2" max="2"/>
-    <col width="16" customWidth="1" style="100" min="3" max="3"/>
+    <col width="21.5" customWidth="1" style="100" min="3" max="3"/>
     <col width="10" customWidth="1" style="100" min="4" max="4"/>
-    <col width="62" customWidth="1" style="100" min="5" max="5"/>
-    <col width="28" customWidth="1" style="100" min="6" max="6"/>
-    <col width="14" customWidth="1" style="100" min="7" max="8"/>
+    <col width="79.5" customWidth="1" style="100" min="5" max="5"/>
+    <col width="84.5" customWidth="1" style="100" min="6" max="6"/>
+    <col width="19.5" customWidth="1" style="100" min="7" max="8"/>
+    <col width="20.5" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>AYARLAR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="74">
-      <c r="A3" s="113" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Ayarlar ve Eşikler (Formüle Sabit Sayı Girilmez)</t>
         </is>
@@ -43823,6 +44177,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="15" customHeight="1" s="74">
       <c r="A37" s="107" t="inlineStr">
         <is>
@@ -43830,6 +44185,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="74">
       <c r="A39" s="111" t="inlineStr">
         <is>
@@ -43843,8 +44199,8 @@
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A39:AN39"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -43862,24 +44218,42 @@
   <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="60" customWidth="1" style="100" min="1" max="1"/>
+    <col width="196.5" customWidth="1" style="100" min="1" max="1"/>
     <col width="40" customWidth="1" style="100" min="2" max="2"/>
+    <col width="13" customWidth="1" style="74" min="3" max="3"/>
+    <col width="13" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="74">
-      <c r="A1" s="112" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>KILAVUZ — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="74">
-      <c r="A3" s="108" t="inlineStr">
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="74">
+      <c r="A3" s="296" t="inlineStr">
         <is>
           <t>Kullanım Kılavuzu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="165" t="inlineStr">
         <is>
@@ -43964,6 +44338,17 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="19.5" customHeight="1" s="74">
       <c r="A28" s="111" t="inlineStr">
         <is>
@@ -43973,19 +44358,20 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A8:AN8"/>
     <mergeCell ref="A6:AN6"/>
     <mergeCell ref="A12:AN12"/>
     <mergeCell ref="A16:AN16"/>
     <mergeCell ref="A15:AN15"/>
     <mergeCell ref="A7:AN7"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:AN11"/>
     <mergeCell ref="A10:AN10"/>
     <mergeCell ref="A28:AN28"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A13:AN13"/>
     <mergeCell ref="A14:AN14"/>
-    <mergeCell ref="A1:AN1"/>
     <mergeCell ref="A9:AN9"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -44001,18 +44387,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
-    <col width="14" customWidth="1" style="74" min="2" max="2"/>
+    <col width="36.5" customWidth="1" style="74" min="2" max="2"/>
     <col width="16" customWidth="1" style="74" min="3" max="3"/>
-    <col width="32" customWidth="1" style="74" min="4" max="4"/>
-    <col width="18" customWidth="1" style="74" min="5" max="5"/>
-    <col width="12" customWidth="1" style="74" min="6" max="6"/>
+    <col width="37.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="18.5" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13.5" customWidth="1" style="74" min="6" max="6"/>
     <col width="18" customWidth="1" style="74" min="7" max="7"/>
-    <col width="22" customWidth="1" style="74" min="8" max="8"/>
+    <col width="22.5" customWidth="1" style="74" min="8" max="8"/>
     <col width="16" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44022,12 +44409,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="208" t="inlineStr">
         <is>
           <t>🔍  KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="284" t="n"/>
+      <c r="D3" s="284" t="n"/>
+      <c r="E3" s="285" t="n"/>
       <c r="G3" s="209" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -44039,6 +44430,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="211" t="inlineStr">
         <is>
@@ -44451,22 +44843,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="228" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="196" t="n"/>
-      <c r="D17" s="196" t="n"/>
       <c r="E17" s="229">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="196" t="n"/>
-      <c r="G17" s="196" t="n"/>
-      <c r="H17" s="196" t="n"/>
-      <c r="I17" s="196" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -44487,7 +44874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
@@ -44532,25 +44919,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="233" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="171" t="n"/>
-      <c r="D6" s="171" t="n"/>
-      <c r="E6" s="171" t="n"/>
-      <c r="F6" s="171" t="n"/>
+      <c r="C6" s="284" t="n"/>
+      <c r="D6" s="284" t="n"/>
+      <c r="E6" s="284" t="n"/>
+      <c r="F6" s="285" t="n"/>
       <c r="H6" s="234" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="171" t="n"/>
-      <c r="J6" s="171" t="n"/>
-      <c r="K6" s="171" t="n"/>
-      <c r="L6" s="171" t="n"/>
+      <c r="I6" s="284" t="n"/>
+      <c r="J6" s="284" t="n"/>
+      <c r="K6" s="284" t="n"/>
+      <c r="L6" s="285" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="171" t="n"/>
@@ -44701,32 +45089,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="171" t="n"/>
-      <c r="D14" s="171" t="n"/>
-      <c r="E14" s="171" t="n"/>
-      <c r="F14" s="171" t="n"/>
+      <c r="C14" s="286" t="n"/>
+      <c r="D14" s="286" t="n"/>
+      <c r="E14" s="286" t="n"/>
+      <c r="F14" s="287" t="n"/>
       <c r="H14" s="241" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="171" t="n"/>
-      <c r="J14" s="171" t="n"/>
-      <c r="K14" s="171" t="n"/>
-      <c r="L14" s="171" t="n"/>
+      <c r="I14" s="288" t="n"/>
+      <c r="J14" s="288" t="n"/>
+      <c r="K14" s="288" t="n"/>
+      <c r="L14" s="289" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="171" t="n"/>
-      <c r="C15" s="171" t="n"/>
-      <c r="D15" s="171" t="n"/>
-      <c r="E15" s="171" t="n"/>
-      <c r="F15" s="171" t="n"/>
-      <c r="H15" s="171" t="n"/>
-      <c r="I15" s="171" t="n"/>
-      <c r="J15" s="171" t="n"/>
-      <c r="K15" s="171" t="n"/>
-      <c r="L15" s="171" t="n"/>
-    </row>
+      <c r="B15" s="290" t="n"/>
+      <c r="C15" s="291" t="n"/>
+      <c r="D15" s="291" t="n"/>
+      <c r="E15" s="291" t="n"/>
+      <c r="F15" s="292" t="n"/>
+      <c r="H15" s="293" t="n"/>
+      <c r="I15" s="294" t="n"/>
+      <c r="J15" s="294" t="n"/>
+      <c r="K15" s="294" t="n"/>
+      <c r="L15" s="295" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="85" t="inlineStr">
         <is>
@@ -44734,6 +45123,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="198" t="inlineStr">
         <is>
@@ -44808,25 +45198,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
-    <col width="24" customWidth="1" style="74" min="2" max="2"/>
-    <col width="22" customWidth="1" style="74" min="3" max="3"/>
-    <col width="27" customWidth="1" style="74" min="4" max="4"/>
-    <col width="29" customWidth="1" style="74" min="5" max="5"/>
-    <col width="20" customWidth="1" style="74" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="23.5" customWidth="1" style="74" min="3" max="3"/>
+    <col width="48.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="43.5" customWidth="1" style="74" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="74" min="6" max="6"/>
     <col width="21" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="74">
-      <c r="A1" s="248" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="249" t="inlineStr">
         <is>
@@ -45286,7 +45688,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45299,22 +45701,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="74" min="1" max="1"/>
-    <col width="52" customWidth="1" style="74" min="2" max="2"/>
-    <col width="34" customWidth="1" style="74" min="3" max="3"/>
+    <col width="89.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="34.5" customWidth="1" style="74" min="3" max="3"/>
     <col width="16" customWidth="1" style="74" min="4" max="4"/>
+    <col width="13" customWidth="1" style="74" min="5" max="5"/>
+    <col width="13" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="74">
-      <c r="A1" s="251" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="252" t="inlineStr">
         <is>
@@ -46026,7 +46443,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46039,24 +46456,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="74" min="1" max="1"/>
-    <col width="36" customWidth="1" style="74" min="2" max="2"/>
-    <col width="48" customWidth="1" style="74" min="3" max="3"/>
-    <col width="34" customWidth="1" style="74" min="4" max="4"/>
-    <col width="30" customWidth="1" style="74" min="5" max="5"/>
+    <col width="30.5" customWidth="1" style="74" min="1" max="1"/>
+    <col width="71.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="160.5" customWidth="1" style="74" min="3" max="3"/>
+    <col width="70.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="50.5" customWidth="1" style="74" min="5" max="5"/>
     <col width="16" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="74">
-      <c r="A1" s="256" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="257" t="inlineStr">
         <is>
@@ -46699,7 +47129,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46712,24 +47142,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="74" min="1" max="1"/>
-    <col width="40" customWidth="1" style="74" min="2" max="2"/>
-    <col width="50" customWidth="1" style="74" min="3" max="3"/>
-    <col width="30" customWidth="1" style="74" min="4" max="4"/>
-    <col width="28" customWidth="1" style="74" min="5" max="5"/>
-    <col width="26" customWidth="1" style="74" min="6" max="6"/>
+    <col width="22.5" customWidth="1" style="74" min="1" max="1"/>
+    <col width="60.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="74" min="3" max="3"/>
+    <col width="40.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="39.5" customWidth="1" style="74" min="5" max="5"/>
+    <col width="27.5" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="74">
-      <c r="A1" s="260" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="261" t="inlineStr">
         <is>
@@ -47244,7 +47687,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47257,23 +47700,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="74" min="1" max="1"/>
-    <col width="32" customWidth="1" style="74" min="2" max="2"/>
-    <col width="54" customWidth="1" style="74" min="3" max="3"/>
-    <col width="34" customWidth="1" style="74" min="4" max="4"/>
+    <col width="20.5" customWidth="1" style="74" min="1" max="1"/>
+    <col width="41.5" customWidth="1" style="74" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="74" min="3" max="3"/>
+    <col width="35.5" customWidth="1" style="74" min="4" max="4"/>
+    <col width="33.5" customWidth="1" style="74" min="5" max="5"/>
     <col width="16" customWidth="1" style="74" min="6" max="6"/>
+    <col width="13" customWidth="1" style="74" min="7" max="7"/>
+    <col width="13" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="13" customWidth="1" style="74" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="74">
-      <c r="A1" s="263" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="74">
+      <c r="A1" s="277" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="278" t="n"/>
+      <c r="C1" s="278" t="n"/>
+      <c r="D1" s="278" t="n"/>
+      <c r="E1" s="278" t="n"/>
+      <c r="F1" s="278" t="n"/>
+      <c r="G1" s="278" t="n"/>
+      <c r="H1" s="278" t="n"/>
+      <c r="I1" s="278" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="264" t="inlineStr">
         <is>
@@ -47820,7 +48277,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
+++ b/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
@@ -4379,7 +4379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="74" min="1" max="1"/>
@@ -4400,14 +4400,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
@@ -4785,7 +4777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="60" customWidth="1" style="100" min="1" max="3"/>
@@ -4806,14 +4798,6 @@
           <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -5088,19 +5072,6 @@
           <t>CALISANLAR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
-      <c r="J1" s="278" t="n"/>
-      <c r="K1" s="278" t="n"/>
-      <c r="L1" s="278" t="n"/>
-      <c r="M1" s="278" t="n"/>
-      <c r="N1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -39758,15 +39729,6 @@
           <t>MOTOR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
-      <c r="J1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -40230,7 +40192,7 @@
         <v/>
       </c>
       <c r="C49" s="134">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T6: Kıdem tazminatı toplam maliyetin "&amp;TEXT(modulT6KidemPay*100,"0")&amp;"% tutarında",IF(modulT6KidemPay&gt;0.5,"kıdem yükü baskın, sözleşme ve tavanı gözden geçirin","maliyet dağılımı dengeli"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T6: Kıdem tazminatı toplam maliyetin "&amp;TEXT(modulT6KidemPay*100,"0")&amp;"% tutarında",IF(modulT6KidemPay&gt;0.5,"kıdem yükü baskın, sözleşme AND tavanı gözden geçirin","maliyet dağılımı dengeli"))</f>
         <v/>
       </c>
     </row>
@@ -40260,7 +40222,7 @@
         <v/>
       </c>
       <c r="C51" s="134">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"O2: Toplam maliyeti en çok etkileyen değişken: "&amp;modulO2TornadoZirve,IF(modulO2TornadoZirve="Ücret Seviyesi","ücret yapısını ve toplu çıkarma planını gözden geçirin","ana değişken netleşti"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"O2: Toplam maliyeti en çok etkileyen değişken: "&amp;modulO2TornadoZirve,IF(modulO2TornadoZirve="Ücret Seviyesi","ücret yapısını AND toplu çıkarma planını gözden geçirin","ana değişken netleşti"))</f>
         <v/>
       </c>
     </row>
@@ -40290,7 +40252,7 @@
         <v/>
       </c>
       <c r="C53" s="134">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"O4: Ortalama kıdem "&amp;modulO4OrtalamaKidemAy&amp;" ay",IF(modulO4OrtalamaKidemAy&gt;KidemYilEsik*12,"kıdem yükü eşik üstünde, çıkarma maliyeti yüksek","kıdem yükü eşik içinde"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"O4: AVERAGE kıdem "&amp;modulO4OrtalamaKidemAy&amp;" ay",IF(modulO4OrtalamaKidemAy&gt;KidemYilEsik*12,"kıdem yükü eşik üstünde, çıkarma maliyeti yüksek","kıdem yükü eşik içinde"))</f>
         <v/>
       </c>
     </row>
@@ -40395,24 +40357,24 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="18">
-    <mergeCell ref="C47:Z47"/>
-    <mergeCell ref="C54:Z54"/>
-    <mergeCell ref="C50:Z50"/>
-    <mergeCell ref="C55:Z55"/>
+    <mergeCell ref="C48:Z48"/>
+    <mergeCell ref="A61:AN61"/>
     <mergeCell ref="C56:Z56"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C49:Z49"/>
     <mergeCell ref="C59:Z59"/>
     <mergeCell ref="C51:Z51"/>
     <mergeCell ref="C46:Z46"/>
-    <mergeCell ref="C52:Z52"/>
-    <mergeCell ref="C48:Z48"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C57:Z57"/>
-    <mergeCell ref="C53:Z53"/>
-    <mergeCell ref="A61:AN61"/>
-    <mergeCell ref="C49:Z49"/>
+    <mergeCell ref="C47:Z47"/>
+    <mergeCell ref="C54:Z54"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="C58:Z58"/>
+    <mergeCell ref="C50:Z50"/>
+    <mergeCell ref="C57:Z57"/>
+    <mergeCell ref="C55:Z55"/>
+    <mergeCell ref="C53:Z53"/>
     <mergeCell ref="C45:Z45"/>
+    <mergeCell ref="C52:Z52"/>
   </mergeCells>
   <conditionalFormatting sqref="B10">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -40466,14 +40428,6 @@
           <t>KONTROL — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -40841,14 +40795,6 @@
           <t>KARAR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="74">
@@ -40929,7 +40875,7 @@
         </is>
       </c>
       <c r="B12" s="142">
-        <f>IF(VeriKaliteSkoru=0,"Girdi eksik; lütfen sarı hücreleri doldurun.",IF(ToplamCikarmaMaliyeti&lt;0,"Çıkarma maliyeti negatif: ücret kayıtlarını kontrol edin.",IF(ToplamCikarmaMaliyeti&gt;CikarmaButceEsik,"Toplam maliyet "&amp;TEXT(ToplamCikarmaMaliyeti,"#,##0")&amp;" ₺ bütçeyi aşıyor; planı revize edin.",IF(ButceKullanimOrani&gt;ButceKullanimEsik,"Bütçenin "&amp;TEXT(ButceKullanimOrani,"0.0%")&amp;" kullanılıyor; kaynak planına ihtiyaç var.",IF(OrtalamaKidemYil&gt;KidemYilEsik,"Ortalama kıdem "&amp;TEXT(OrtalamaKidemYil,"0")&amp;" yıl eşik üstünde; kıdem yükü yüksek.","Kıdem, ihbar ve izin yükü bütçe ve eşikler içinde kabul edilebilir.")))))</f>
+        <f>IF(VeriKaliteSkoru=0,"Girdi eksik; lütfen sarı hücreleri doldurun.",IF(ToplamCikarmaMaliyeti&lt;0,"Çıkarma maliyeti negatif: ücret kayıtlarını kontrol edin.",IF(ToplamCikarmaMaliyeti&gt;CikarmaButceEsik,"Toplam maliyet "&amp;TEXT(ToplamCikarmaMaliyeti,"#,##0")&amp;" ₺ bütçeyi aşıyor; planı revize edin.",IF(ButceKullanimOrani&gt;ButceKullanimEsik,"Bütçenin "&amp;TEXT(ButceKullanimOrani,"0.0%")&amp;" kullanılıyor; kaynak planına ihtiyaç var.",IF(OrtalamaKidemYil&gt;KidemYilEsik,"AVERAGE kıdem "&amp;TEXT(OrtalamaKidemYil,"0")&amp;" yıl eşik üstünde; kıdem yükü yüksek.","Kıdem, ihbar AND izin yükü bütçe AND eşikler içinde kabul edilebilir.")))))</f>
         <v/>
       </c>
     </row>
@@ -40943,19 +40889,19 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="74">
       <c r="A15" s="142">
-        <f>IF(OR(KararSonuc="VERİ YOK",KararSonuc="DURDUR"),"Çalışan ücret ve tarih kayıtlarını bordroyla mutabakat edin; tavanı ve bütçeyi yeniden değerlendirin",IF(ButceKullanimOrani&gt;ButceKullanimEsik,"Çıkarma planını dönemlere yayın ve bütçeyi revize edin","Çıkarma planını ve ödeme takvimini bütçeye işleyin"))</f>
+        <f>IF(OR(KararSonuc="VERİ YOK",KararSonuc="DURDUR"),"Çalışan ücret AND tarih kayıtlarını bordroyla mutabakat edin; tavanı AND bütçeyi yeniden değerlendirin",IF(ButceKullanimOrani&gt;ButceKullanimEsik,"Çıkarma planını dönemlere yayın AND bütçeyi revize edin","Çıkarma planını AND ödeme takvimini bütçeye işleyin"))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="74">
       <c r="A16" s="142">
-        <f>IF(OrtalamaKidemYil&gt;KidemYilEsik,"Kıdem yükü yüksek çalışanlar için tavan ve sözleşme koşullarını teyit edin","Kıdem yükü kabul edilebilir seviyede")</f>
+        <f>IF(OrtalamaKidemYil&gt;KidemYilEsik,"Kıdem yükü yüksek çalışanlar için tavan AND sözleşme koşullarını teyit edin","Kıdem yükü kabul edilebilir seviyede")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="74">
       <c r="A17" s="142">
-        <f>IF(AnomaliCalisanAdedi&gt;0,"Anomali ücretli çalışanların bordro ve sözleşmelerini inceleyin","Ücret dağılımı tutarlı")</f>
+        <f>IF(AnomaliCalisanAdedi&gt;0,"Anomali ücretli çalışanların bordro AND sözleşmelerini inceleyin","Ücret dağılımı tutarlı")</f>
         <v/>
       </c>
     </row>
@@ -40979,8 +40925,8 @@
   <mergeCells count="6">
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
@@ -41031,14 +40977,6 @@
           <t>SENARYO DUYARLILIK — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -41395,7 +41333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="146.5" customWidth="1" style="100" min="1" max="1"/>
@@ -41416,14 +41354,6 @@
           <t>KIDEM–İHBAR YÜKÜ VE ÇIKARMA MALİYETİ RAPORU</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="74">
       <c r="A2" s="104">
@@ -41573,7 +41503,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" s="74">
       <c r="A24" s="157">
-        <f>IF(OrtalamaKidemYil&gt;KidemYilEsik,"Ortalama kıdem eşik üstünde; kıdem yükü yüksek.","Kıdem yükü kabul edilebilir seviyede.")</f>
+        <f>IF(OrtalamaKidemYil&gt;KidemYilEsik,"AVERAGE kıdem eşik üstünde; kıdem yükü yüksek.","Kıdem yükü kabul edilebilir seviyede.")</f>
         <v/>
       </c>
     </row>
@@ -41688,14 +41618,6 @@
           <t>ORNEK VERI — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -41847,7 +41769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="74" min="1" max="1"/>
@@ -41868,14 +41790,6 @@
           <t>KURALLAR — eski35_kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici_uretildi</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="74">
@@ -41980,7 +41894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
@@ -42111,7 +42025,7 @@
       <c r="I7" s="171" t="n"/>
       <c r="J7" s="171" t="n"/>
       <c r="K7" s="182">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="171" t="n"/>
@@ -42416,11 +42330,11 @@
         </is>
       </c>
       <c r="I19" s="271">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="272">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="196" t="inlineStr"/>
@@ -42566,7 +42480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="74" min="1" max="1"/>
@@ -42586,13 +42500,6 @@
           <t>VAKALAR — eski35_kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici_uretildi</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -42720,14 +42627,6 @@
           <t>DEGISIKLIK KAYDI — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -42821,14 +42720,6 @@
           <t>LISTELER — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -42909,13 +42800,6 @@
           <t>AYARLAR — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -44236,14 +44120,6 @@
           <t>KILAVUZ — KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALİYETİ HESAPLAYICI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
@@ -44387,7 +44263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
@@ -44851,7 +44727,7 @@
         </is>
       </c>
       <c r="E17" s="229">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -44874,7 +44750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
@@ -45041,7 +44917,7 @@
       <c r="C11" s="171" t="n"/>
       <c r="D11" s="171" t="n"/>
       <c r="E11" s="276">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="171" t="n"/>
@@ -45198,7 +45074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="74" min="1" max="1"/>
@@ -45219,14 +45095,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
@@ -45701,7 +45569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="74" min="1" max="1"/>
@@ -45722,14 +45590,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
@@ -46456,7 +46316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" style="74" min="1" max="1"/>
@@ -46477,14 +46337,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
@@ -47142,7 +46994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" style="74" min="1" max="1"/>
@@ -47163,14 +47015,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
@@ -47700,7 +47544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" style="74" min="1" max="1"/>
@@ -47721,14 +47565,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="278" t="n"/>
-      <c r="C1" s="278" t="n"/>
-      <c r="D1" s="278" t="n"/>
-      <c r="E1" s="278" t="n"/>
-      <c r="F1" s="278" t="n"/>
-      <c r="G1" s="278" t="n"/>
-      <c r="H1" s="278" t="n"/>
-      <c r="I1" s="278" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">

--- a/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
+++ b/EXCELARSIV_PRODUCTS/kidem-ihbar-yuku-ve-personel-cikarma-maliyeti-hesaplayici/KidemIhbarYukuVePersonelCikarmaMaliyetiHesaplayici.xlsx
@@ -141,7 +141,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="101">
+  <fonts count="137">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -770,8 +770,220 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -981,8 +1193,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -1344,6 +1580,348 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1355,7 +1933,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="394">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2108,6 +2686,235 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="21" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="21" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="21" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="21" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="104" fillId="21" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="106" fillId="21" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="104" fillId="21" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="21" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="10" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="10" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="54" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="79" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="54" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="79" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="118" fillId="10" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="119" fillId="10" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="10" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="21" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="20" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="122" fillId="21" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="21" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="122" fillId="21" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="128" fillId="20" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="21" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="20" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="21" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="21" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="130" fillId="15" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="14" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="131" fillId="21" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="132" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="21" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="121" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="133" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="133" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="15" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="14" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="21" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="21" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="21" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4401,7 +5208,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="244" t="inlineStr">
         <is>
@@ -4666,7 +5472,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="74">
       <c r="A26" s="247" t="inlineStr">
         <is>
@@ -4799,7 +5604,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -4836,7 +5640,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="74">
       <c r="A10" s="105" t="inlineStr">
         <is>
@@ -4847,7 +5650,6 @@
     <row r="11" ht="15" customHeight="1" s="74"/>
     <row r="12" ht="15" customHeight="1" s="74"/>
     <row r="13" ht="15" customHeight="1" s="74"/>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="74">
       <c r="A15" s="106" t="inlineStr">
         <is>
@@ -4908,7 +5710,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -4965,7 +5766,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="74">
       <c r="A12" s="110" t="inlineStr">
         <is>
@@ -5008,7 +5808,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="74">
       <c r="A19" s="111" t="inlineStr">
         <is>
@@ -5073,7 +5872,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -5081,7 +5879,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="74">
       <c r="A5" s="114" t="inlineStr">
         <is>
@@ -21690,7 +22487,6 @@
       <c r="E1004" s="121" t="n"/>
       <c r="M1004" s="121" t="n"/>
     </row>
-    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="74">
       <c r="A1006" s="111" t="inlineStr">
         <is>
@@ -39730,7 +40526,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -39738,8 +40533,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="74">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -39916,9 +40709,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="74">
       <c r="A25" s="113" t="inlineStr">
         <is>
@@ -40113,7 +40903,6 @@
         <v/>
       </c>
     </row>
-    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="74">
       <c r="A44" s="113" t="inlineStr">
         <is>
@@ -40346,7 +41135,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
     <row r="61" ht="19.5" customHeight="1" s="74">
       <c r="A61" s="111" t="inlineStr">
         <is>
@@ -40429,7 +41217,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -40437,7 +41224,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -40445,7 +41231,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="74">
       <c r="A7" s="136" t="inlineStr">
         <is>
@@ -40556,7 +41341,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="74">
       <c r="A18" s="135" t="inlineStr">
         <is>
@@ -40608,7 +41392,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="74">
       <c r="A24" s="136" t="inlineStr">
         <is>
@@ -40620,7 +41403,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="19.5" customHeight="1" s="74">
       <c r="A26" s="111" t="inlineStr">
         <is>
@@ -40796,7 +41578,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="74">
       <c r="A3" s="113" t="inlineStr">
         <is>
@@ -40804,7 +41585,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -40856,7 +41636,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="18.75" customHeight="1" s="74">
       <c r="A11" s="113" t="inlineStr">
         <is>
@@ -40879,7 +41658,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="74">
       <c r="A14" s="135" t="inlineStr">
         <is>
@@ -40911,8 +41689,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="19.5" customHeight="1" s="74">
       <c r="A21" s="111" t="inlineStr">
         <is>
@@ -40978,7 +41754,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -40986,7 +41761,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -41124,7 +41898,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="74">
       <c r="A11" s="135" t="inlineStr">
         <is>
@@ -41231,7 +42004,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="74">
       <c r="A16" s="135" t="inlineStr">
         <is>
@@ -41272,7 +42044,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="19.5" customHeight="1" s="74">
       <c r="A21" s="111" t="inlineStr">
         <is>
@@ -41367,7 +42138,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="135" t="inlineStr">
         <is>
@@ -41430,7 +42200,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="74">
       <c r="A12" s="135" t="inlineStr">
         <is>
@@ -41444,7 +42213,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="74">
       <c r="A15" s="135" t="inlineStr">
         <is>
@@ -41487,7 +42255,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="74">
       <c r="A22" s="135" t="inlineStr">
         <is>
@@ -41507,7 +42274,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="74">
       <c r="A26" s="135" t="inlineStr">
         <is>
@@ -41533,7 +42299,6 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="74">
       <c r="A31" s="158">
         <f>firmaUnvani &amp; " | " &amp; TEXT(raporTarihi,"gg.aa.yyyy") &amp; " | Rev 1.0"</f>
@@ -41619,7 +42384,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -41634,7 +42398,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1" s="74">
       <c r="A6" s="114" t="inlineStr">
         <is>
@@ -41739,8 +42502,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12" ht="19.5" customHeight="1" s="74">
       <c r="A12" s="111" t="inlineStr">
         <is>
@@ -41791,7 +42552,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="74">
       <c r="A3" s="100" t="inlineStr">
         <is>
@@ -41897,554 +42657,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="74" min="1" max="1"/>
-    <col width="92.5" customWidth="1" style="74" min="2" max="2"/>
-    <col width="15" customWidth="1" style="74" min="3" max="3"/>
-    <col width="15.5" customWidth="1" style="74" min="4" max="4"/>
-    <col width="36.5" customWidth="1" style="74" min="5" max="5"/>
-    <col width="18" customWidth="1" style="74" min="6" max="6"/>
-    <col width="11.5" customWidth="1" style="74" min="7" max="7"/>
-    <col width="75.5" customWidth="1" style="74" min="8" max="8"/>
-    <col width="15" customWidth="1" style="74" min="9" max="9"/>
-    <col width="15.5" customWidth="1" style="74" min="10" max="10"/>
-    <col width="81.5" customWidth="1" style="74" min="11" max="11"/>
-    <col width="18" customWidth="1" style="74" min="12" max="12"/>
-    <col width="18" customWidth="1" style="74" min="13" max="13"/>
-    <col width="13" customWidth="1" style="74" min="14" max="14"/>
+    <col width="12" customWidth="1" style="74" min="1" max="1"/>
+    <col width="17" customWidth="1" style="74" min="2" max="2"/>
+    <col width="12" customWidth="1" style="74" min="3" max="3"/>
+    <col width="11" customWidth="1" style="74" min="4" max="4"/>
+    <col width="17" customWidth="1" style="74" min="5" max="5"/>
+    <col width="12" customWidth="1" style="74" min="6" max="6"/>
+    <col width="11" customWidth="1" style="74" min="7" max="7"/>
+    <col width="17" customWidth="1" style="74" min="8" max="8"/>
+    <col width="13" customWidth="1" style="74" min="9" max="9"/>
+    <col width="11" customWidth="1" style="74" min="10" max="10"/>
+    <col width="17" customWidth="1" style="74" min="11" max="11"/>
+    <col width="14" customWidth="1" style="74" min="12" max="12"/>
+    <col width="12" customWidth="1" style="74" min="13" max="13"/>
+    <col width="6" customWidth="1" style="74" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="74">
+      <c r="A1" s="297" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="166" t="inlineStr">
+    <row r="2" ht="28" customHeight="1" s="74">
+      <c r="B2" s="298" t="inlineStr">
         <is>
           <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI</t>
         </is>
       </c>
-      <c r="L2" s="167" t="inlineStr">
+      <c r="L2" s="299" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="168" t="inlineStr">
+      <c r="M2" s="300" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="169" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="74">
+      <c r="B3" s="301" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: İnsan kaynakları yöneticileri, işverenler, mali müşavirler ve personel çıkarma planı yapan işletme sahipleri · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="170" t="inlineStr">
+    <row r="4" ht="10" customHeight="1" s="74"/>
+    <row r="5" ht="20" customHeight="1" s="74">
+      <c r="B5" s="302" t="inlineStr">
         <is>
           <t>TOPLAM İŞLEM HACMİ</t>
         </is>
       </c>
-      <c r="C5" s="171" t="n"/>
-      <c r="D5" s="172" t="inlineStr">
+      <c r="C5" s="303" t="n"/>
+      <c r="D5" s="304" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="173" t="inlineStr">
+      <c r="E5" s="305" t="inlineStr">
         <is>
           <t>OPERASYONEL MALİYET</t>
         </is>
       </c>
-      <c r="F5" s="171" t="n"/>
-      <c r="G5" s="174" t="inlineStr">
+      <c r="F5" s="303" t="n"/>
+      <c r="G5" s="306" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="170" t="inlineStr">
+      <c r="H5" s="307" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="171" t="n"/>
-      <c r="J5" s="175" t="inlineStr">
+      <c r="I5" s="303" t="n"/>
+      <c r="J5" s="308" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="176" t="inlineStr">
+      <c r="K5" s="309" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="171" t="n"/>
-      <c r="M5" s="172" t="inlineStr">
+      <c r="L5" s="303" t="n"/>
+      <c r="M5" s="310" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="177" t="n"/>
-      <c r="C6" s="171" t="n"/>
-      <c r="D6" s="171" t="n"/>
-      <c r="E6" s="178" t="n"/>
-      <c r="F6" s="171" t="n"/>
-      <c r="G6" s="171" t="n"/>
-      <c r="H6" s="177" t="n"/>
-      <c r="I6" s="171" t="n"/>
-      <c r="J6" s="171" t="n"/>
-      <c r="K6" s="179" t="n"/>
-      <c r="L6" s="171" t="n"/>
-      <c r="M6" s="171" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="267">
+    <row r="6" ht="6" customHeight="1" s="74">
+      <c r="B6" s="311" t="n"/>
+      <c r="C6" s="312" t="n"/>
+      <c r="D6" s="313" t="n"/>
+      <c r="E6" s="314" t="n"/>
+      <c r="F6" s="312" t="n"/>
+      <c r="G6" s="313" t="n"/>
+      <c r="H6" s="315" t="n"/>
+      <c r="I6" s="312" t="n"/>
+      <c r="J6" s="313" t="n"/>
+      <c r="K6" s="316" t="n"/>
+      <c r="L6" s="312" t="n"/>
+      <c r="M6" s="313" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="74">
+      <c r="B7" s="317">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="171" t="n"/>
-      <c r="D7" s="171" t="n"/>
-      <c r="E7" s="268">
+      <c r="C7" s="312" t="n"/>
+      <c r="D7" s="313" t="n"/>
+      <c r="E7" s="318">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="171" t="n"/>
-      <c r="G7" s="171" t="n"/>
-      <c r="H7" s="267">
+      <c r="F7" s="312" t="n"/>
+      <c r="G7" s="313" t="n"/>
+      <c r="H7" s="319">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="171" t="n"/>
-      <c r="J7" s="171" t="n"/>
-      <c r="K7" s="182">
+      <c r="I7" s="312" t="n"/>
+      <c r="J7" s="313" t="n"/>
+      <c r="K7" s="320">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="171" t="n"/>
-      <c r="M7" s="171" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="177" t="n"/>
-      <c r="C8" s="171" t="n"/>
-      <c r="D8" s="171" t="n"/>
-      <c r="E8" s="178" t="n"/>
-      <c r="F8" s="171" t="n"/>
-      <c r="G8" s="171" t="n"/>
-      <c r="H8" s="177" t="n"/>
-      <c r="I8" s="171" t="n"/>
-      <c r="J8" s="171" t="n"/>
-      <c r="K8" s="179" t="n"/>
-      <c r="L8" s="171" t="n"/>
-      <c r="M8" s="171" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="183" t="inlineStr">
+      <c r="L7" s="312" t="n"/>
+      <c r="M7" s="313" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1" s="74">
+      <c r="B8" s="311" t="n"/>
+      <c r="C8" s="312" t="n"/>
+      <c r="D8" s="313" t="n"/>
+      <c r="E8" s="314" t="n"/>
+      <c r="F8" s="312" t="n"/>
+      <c r="G8" s="313" t="n"/>
+      <c r="H8" s="315" t="n"/>
+      <c r="I8" s="312" t="n"/>
+      <c r="J8" s="313" t="n"/>
+      <c r="K8" s="316" t="n"/>
+      <c r="L8" s="312" t="n"/>
+      <c r="M8" s="313" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="74">
+      <c r="B9" s="321" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="171" t="n"/>
-      <c r="D9" s="171" t="n"/>
-      <c r="E9" s="184" t="inlineStr">
+      <c r="C9" s="322" t="n"/>
+      <c r="D9" s="323" t="n"/>
+      <c r="E9" s="324" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="171" t="n"/>
-      <c r="G9" s="171" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
+      <c r="F9" s="322" t="n"/>
+      <c r="G9" s="323" t="n"/>
+      <c r="H9" s="325" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="171" t="n"/>
-      <c r="J9" s="171" t="n"/>
-      <c r="K9" s="185" t="inlineStr">
+      <c r="I9" s="322" t="n"/>
+      <c r="J9" s="323" t="n"/>
+      <c r="K9" s="326" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="171" t="n"/>
-      <c r="M9" s="171" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="98" t="inlineStr">
+      <c r="L9" s="322" t="n"/>
+      <c r="M9" s="323" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" s="74"/>
+    <row r="11" ht="24" customHeight="1" s="74">
+      <c r="B11" s="327" t="inlineStr">
         <is>
           <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="186" t="inlineStr">
+      <c r="F11" s="328" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="98" t="inlineStr">
+      <c r="H11" s="327" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="97" t="inlineStr">
+    <row r="12" ht="18" customHeight="1" s="74">
+      <c r="B12" s="169" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="97" t="inlineStr">
+      <c r="H12" s="169" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="187" t="inlineStr">
+    <row r="13" ht="8" customHeight="1" s="74"/>
+    <row r="14" ht="24" customHeight="1" s="74">
+      <c r="B14" s="329" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="187" t="inlineStr">
+      <c r="C14" s="329" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="187" t="inlineStr">
+      <c r="D14" s="329" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="187" t="inlineStr">
+      <c r="E14" s="329" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="188" t="inlineStr">
+      <c r="H14" s="330" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="188" t="inlineStr">
+      <c r="I14" s="331" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="188" t="inlineStr">
+      <c r="J14" s="331" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="188" t="inlineStr">
+      <c r="K14" s="331" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="188" t="inlineStr">
+      <c r="L14" s="331" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="97" t="inlineStr">
+      <c r="M14" s="331" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="74">
+      <c r="B15" s="332" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="97" t="n">
+      <c r="C15" s="332" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="97" t="n">
+      <c r="D15" s="332" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="97" t="n">
+      <c r="E15" s="332" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="189" t="inlineStr">
+      <c r="H15" s="333" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="269">
+      <c r="I15" s="334">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="270">
+      <c r="J15" s="335">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="191" t="inlineStr">
+      <c r="K15" s="336" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="175" t="inlineStr">
+      <c r="L15" s="337" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="97" t="inlineStr">
+      <c r="M15" s="338" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="74">
+      <c r="B16" s="339" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="97" t="n">
+      <c r="C16" s="339" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="97" t="n">
+      <c r="D16" s="339" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="97" t="n">
+      <c r="E16" s="339" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="189" t="inlineStr">
+      <c r="H16" s="340" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="269">
+      <c r="I16" s="341">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="270">
+      <c r="J16" s="342">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="191" t="inlineStr">
+      <c r="K16" s="343" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="172" t="inlineStr">
+      <c r="L16" s="344" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="97" t="inlineStr">
+      <c r="M16" s="345" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="74">
+      <c r="B17" s="332" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="97" t="n">
+      <c r="C17" s="332" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="97" t="n">
+      <c r="D17" s="332" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="97" t="n">
+      <c r="E17" s="332" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="189" t="inlineStr">
+      <c r="H17" s="333" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="269">
+      <c r="I17" s="334">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="270">
+      <c r="J17" s="335">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="191" t="inlineStr">
+      <c r="K17" s="336" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="192" t="inlineStr">
+      <c r="L17" s="346" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="97" t="inlineStr">
+      <c r="M17" s="338" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="74">
+      <c r="B18" s="339" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="97" t="n">
+      <c r="C18" s="339" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="97" t="n">
+      <c r="D18" s="339" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="97" t="n">
+      <c r="E18" s="339" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="189" t="inlineStr">
+      <c r="H18" s="340" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="269">
+      <c r="I18" s="341">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="270">
+      <c r="J18" s="342">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="191" t="inlineStr">
+      <c r="K18" s="343" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="175" t="inlineStr">
+      <c r="L18" s="347" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="97" t="inlineStr">
+      <c r="M18" s="345" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="74">
+      <c r="B19" s="332" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="97" t="n">
+      <c r="C19" s="332" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="97" t="n">
+      <c r="D19" s="332" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="97" t="n">
+      <c r="E19" s="332" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="193" t="inlineStr">
+      <c r="H19" s="348" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="271">
+      <c r="I19" s="349">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="272">
+      <c r="J19" s="350">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="196" t="inlineStr"/>
-      <c r="L19" s="197" t="inlineStr">
+      <c r="K19" s="351" t="inlineStr"/>
+      <c r="L19" s="352" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="97" t="inlineStr">
+      <c r="M19" s="352" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="74">
+      <c r="B20" s="339" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="97" t="n">
+      <c r="C20" s="339" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="97" t="n">
+      <c r="D20" s="339" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="97" t="n">
+      <c r="E20" s="339" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="198" t="inlineStr">
+    <row r="21" ht="14" customHeight="1" s="74"/>
+    <row r="22" ht="24" customHeight="1" s="74">
+      <c r="B22" s="353" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="198" t="inlineStr">
+      <c r="C22" s="303" t="n"/>
+      <c r="D22" s="303" t="n"/>
+      <c r="E22" s="354" t="n"/>
+      <c r="F22" s="353" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="199" t="inlineStr">
+      <c r="G22" s="303" t="n"/>
+      <c r="H22" s="303" t="n"/>
+      <c r="I22" s="354" t="n"/>
+      <c r="K22" s="355" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="200" t="n"/>
-      <c r="M22" s="200" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="82" t="inlineStr">
+      <c r="L22" s="356" t="n"/>
+      <c r="M22" s="357" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="74">
+      <c r="B23" s="358" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="97" t="inlineStr">
+      <c r="C23" s="312" t="n"/>
+      <c r="D23" s="312" t="n"/>
+      <c r="E23" s="313" t="n"/>
+      <c r="F23" s="359" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="201" t="inlineStr">
+      <c r="G23" s="312" t="n"/>
+      <c r="H23" s="312" t="n"/>
+      <c r="I23" s="360" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="202" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="200" t="n"/>
-      <c r="M23" s="200" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="83" t="inlineStr">
+      <c r="K23" s="361" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="362" t="n"/>
+      <c r="M23" s="363" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="74">
+      <c r="B24" s="364" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="97" t="inlineStr">
+      <c r="C24" s="312" t="n"/>
+      <c r="D24" s="312" t="n"/>
+      <c r="E24" s="313" t="n"/>
+      <c r="F24" s="359" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="201" t="inlineStr">
+      <c r="G24" s="312" t="n"/>
+      <c r="H24" s="312" t="n"/>
+      <c r="I24" s="360" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="203" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="204" t="inlineStr">
+      <c r="K24" s="365" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="74">
+      <c r="B25" s="366" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="82" t="inlineStr">
+      <c r="C25" s="312" t="n"/>
+      <c r="D25" s="312" t="n"/>
+      <c r="E25" s="313" t="n"/>
+      <c r="F25" s="337" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="205" t="inlineStr">
+      <c r="G25" s="367" t="n"/>
+      <c r="H25" s="367" t="n"/>
+      <c r="I25" s="367" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="74">
+      <c r="B26" s="368" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="206" t="inlineStr">
+      <c r="C26" s="312" t="n"/>
+      <c r="D26" s="312" t="n"/>
+      <c r="E26" s="313" t="n"/>
+      <c r="F26" s="369" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -42452,23 +43243,29 @@
       <c r="G26" s="279" t="n"/>
       <c r="H26" s="279" t="n"/>
       <c r="I26" s="280" t="n"/>
-      <c r="K26" s="207" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="370" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="74">
+      <c r="B27" s="371" t="n"/>
+      <c r="C27" s="322" t="n"/>
+      <c r="D27" s="322" t="n"/>
+      <c r="E27" s="323" t="n"/>
       <c r="F27" s="281" t="n"/>
       <c r="G27" s="282" t="n"/>
       <c r="H27" s="282" t="n"/>
       <c r="I27" s="283" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42501,7 +43298,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -42509,7 +43305,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="100" t="inlineStr">
         <is>
@@ -42628,7 +43423,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -42636,7 +43430,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="74">
       <c r="A5" s="114" t="inlineStr">
         <is>
@@ -42671,7 +43464,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="19.5" customHeight="1" s="74">
       <c r="A8" s="111" t="inlineStr">
         <is>
@@ -42721,7 +43513,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -42736,7 +43527,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="74">
       <c r="A6" s="115" t="inlineStr">
         <is>
@@ -42751,8 +43541,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10" ht="19.5" customHeight="1" s="74">
       <c r="A10" s="111" t="inlineStr">
         <is>
@@ -42801,7 +43589,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -44061,7 +44848,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37" ht="15" customHeight="1" s="74">
       <c r="A37" s="107" t="inlineStr">
         <is>
@@ -44069,7 +44855,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="74">
       <c r="A39" s="111" t="inlineStr">
         <is>
@@ -44121,7 +44906,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="74">
       <c r="A3" s="296" t="inlineStr">
         <is>
@@ -44129,7 +44913,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="74">
       <c r="A5" s="165" t="inlineStr">
         <is>
@@ -44214,17 +44997,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="19.5" customHeight="1" s="74">
       <c r="A28" s="111" t="inlineStr">
         <is>
@@ -44285,7 +45057,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="208" t="inlineStr">
         <is>
@@ -44306,7 +45077,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="211" t="inlineStr">
         <is>
@@ -44719,7 +45489,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="228" t="inlineStr">
         <is>
@@ -44750,54 +45519,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="74" min="1" max="1"/>
+    <col width="12" customWidth="1" style="74" min="1" max="1"/>
     <col width="24" customWidth="1" style="74" min="2" max="2"/>
-    <col width="15" customWidth="1" style="74" min="3" max="3"/>
-    <col width="15" customWidth="1" style="74" min="4" max="4"/>
-    <col width="22" customWidth="1" style="74" min="5" max="5"/>
-    <col width="6" customWidth="1" style="74" min="6" max="6"/>
+    <col width="14" customWidth="1" style="74" min="3" max="3"/>
+    <col width="14" customWidth="1" style="74" min="4" max="4"/>
+    <col width="16" customWidth="1" style="74" min="5" max="5"/>
+    <col width="14" customWidth="1" style="74" min="6" max="6"/>
     <col width="6" customWidth="1" style="74" min="7" max="7"/>
     <col width="24" customWidth="1" style="74" min="8" max="8"/>
-    <col width="15" customWidth="1" style="74" min="9" max="9"/>
-    <col width="15" customWidth="1" style="74" min="10" max="10"/>
-    <col width="22" customWidth="1" style="74" min="11" max="11"/>
-    <col width="6" customWidth="1" style="74" min="12" max="12"/>
+    <col width="14" customWidth="1" style="74" min="9" max="9"/>
+    <col width="14" customWidth="1" style="74" min="10" max="10"/>
+    <col width="16" customWidth="1" style="74" min="11" max="11"/>
+    <col width="14" customWidth="1" style="74" min="12" max="12"/>
+    <col width="6" customWidth="1" style="74" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="74">
+      <c r="A1" s="297" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1" s="74">
       <c r="B2" s="230" t="inlineStr">
         <is>
           <t>KIDEM–İHBAR YÜKÜ VE PERSONEL ÇIKARMA MALIYETI HESAPLAYICI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="231" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="74">
+      <c r="B3" s="372" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · İnsan kaynakları yöneticileri, işverenler, mali müşavirler ve personel çıkarma planı yapan işletme sahipleri</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="232" t="inlineStr">
+    <row r="4" ht="20" customHeight="1" s="74">
+      <c r="B4" s="373" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="233" t="inlineStr">
+    <row r="5" ht="12" customHeight="1" s="74"/>
+    <row r="6" ht="26" customHeight="1" s="74">
+      <c r="B6" s="374" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -44806,7 +45576,7 @@
       <c r="D6" s="284" t="n"/>
       <c r="E6" s="284" t="n"/>
       <c r="F6" s="285" t="n"/>
-      <c r="H6" s="234" t="inlineStr">
+      <c r="H6" s="375" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -44816,151 +45586,151 @@
       <c r="K6" s="284" t="n"/>
       <c r="L6" s="285" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="171" t="n"/>
-      <c r="C7" s="171" t="n"/>
-      <c r="D7" s="171" t="n"/>
-      <c r="E7" s="171" t="n"/>
-      <c r="F7" s="171" t="n"/>
-      <c r="H7" s="171" t="n"/>
-      <c r="I7" s="171" t="n"/>
-      <c r="J7" s="171" t="n"/>
-      <c r="K7" s="171" t="n"/>
-      <c r="L7" s="171" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="235" t="inlineStr">
+    <row r="7" ht="22" customHeight="1" s="74">
+      <c r="B7" s="376" t="n"/>
+      <c r="C7" s="312" t="n"/>
+      <c r="D7" s="312" t="n"/>
+      <c r="E7" s="312" t="n"/>
+      <c r="F7" s="377" t="n"/>
+      <c r="H7" s="378" t="n"/>
+      <c r="I7" s="312" t="n"/>
+      <c r="J7" s="312" t="n"/>
+      <c r="K7" s="312" t="n"/>
+      <c r="L7" s="379" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="74">
+      <c r="B8" s="380" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="171" t="n"/>
-      <c r="D8" s="171" t="n"/>
-      <c r="E8" s="236" t="inlineStr">
+      <c r="C8" s="312" t="n"/>
+      <c r="D8" s="312" t="n"/>
+      <c r="E8" s="381" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="171" t="n"/>
-      <c r="H8" s="235" t="inlineStr">
+      <c r="F8" s="377" t="n"/>
+      <c r="H8" s="382" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="171" t="n"/>
-      <c r="J8" s="171" t="n"/>
-      <c r="K8" s="237" t="inlineStr">
+      <c r="I8" s="312" t="n"/>
+      <c r="J8" s="312" t="n"/>
+      <c r="K8" s="383" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="171" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="235" t="inlineStr">
+      <c r="L8" s="379" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="74">
+      <c r="B9" s="380" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="171" t="n"/>
-      <c r="D9" s="171" t="n"/>
-      <c r="E9" s="274">
+      <c r="C9" s="312" t="n"/>
+      <c r="D9" s="312" t="n"/>
+      <c r="E9" s="384">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="171" t="n"/>
-      <c r="H9" s="235" t="inlineStr">
+      <c r="F9" s="377" t="n"/>
+      <c r="H9" s="382" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="171" t="n"/>
-      <c r="J9" s="171" t="n"/>
-      <c r="K9" s="274">
+      <c r="I9" s="312" t="n"/>
+      <c r="J9" s="312" t="n"/>
+      <c r="K9" s="384">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="171" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="235" t="inlineStr">
+      <c r="L9" s="379" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="74">
+      <c r="B10" s="380" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="171" t="n"/>
-      <c r="D10" s="171" t="n"/>
-      <c r="E10" s="275">
+      <c r="C10" s="312" t="n"/>
+      <c r="D10" s="312" t="n"/>
+      <c r="E10" s="385">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="171" t="n"/>
-      <c r="H10" s="235" t="inlineStr">
+      <c r="F10" s="377" t="n"/>
+      <c r="H10" s="382" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="171" t="n"/>
-      <c r="J10" s="171" t="n"/>
-      <c r="K10" s="275">
+      <c r="I10" s="312" t="n"/>
+      <c r="J10" s="312" t="n"/>
+      <c r="K10" s="385">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="171" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="235" t="inlineStr">
+      <c r="L10" s="379" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="74">
+      <c r="B11" s="380" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="171" t="n"/>
-      <c r="D11" s="171" t="n"/>
-      <c r="E11" s="276">
+      <c r="C11" s="312" t="n"/>
+      <c r="D11" s="312" t="n"/>
+      <c r="E11" s="386">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="171" t="n"/>
-      <c r="H11" s="235" t="inlineStr">
+      <c r="F11" s="377" t="n"/>
+      <c r="H11" s="382" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="171" t="n"/>
-      <c r="J11" s="171" t="n"/>
-      <c r="K11" s="239" t="inlineStr">
+      <c r="I11" s="312" t="n"/>
+      <c r="J11" s="312" t="n"/>
+      <c r="K11" s="387" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="171" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="171" t="n"/>
-      <c r="C12" s="171" t="n"/>
-      <c r="D12" s="171" t="n"/>
-      <c r="E12" s="171" t="n"/>
-      <c r="F12" s="171" t="n"/>
-      <c r="H12" s="171" t="n"/>
-      <c r="I12" s="171" t="n"/>
-      <c r="J12" s="171" t="n"/>
-      <c r="K12" s="171" t="n"/>
-      <c r="L12" s="171" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="171" t="n"/>
-      <c r="C13" s="171" t="n"/>
-      <c r="D13" s="171" t="n"/>
-      <c r="E13" s="171" t="n"/>
-      <c r="F13" s="171" t="n"/>
-      <c r="H13" s="171" t="n"/>
-      <c r="I13" s="171" t="n"/>
-      <c r="J13" s="171" t="n"/>
-      <c r="K13" s="171" t="n"/>
-      <c r="L13" s="171" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="240" t="inlineStr">
+      <c r="L11" s="379" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="74">
+      <c r="B12" s="376" t="n"/>
+      <c r="C12" s="312" t="n"/>
+      <c r="D12" s="312" t="n"/>
+      <c r="E12" s="312" t="n"/>
+      <c r="F12" s="377" t="n"/>
+      <c r="H12" s="378" t="n"/>
+      <c r="I12" s="312" t="n"/>
+      <c r="J12" s="312" t="n"/>
+      <c r="K12" s="312" t="n"/>
+      <c r="L12" s="379" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="74">
+      <c r="B13" s="376" t="n"/>
+      <c r="C13" s="312" t="n"/>
+      <c r="D13" s="312" t="n"/>
+      <c r="E13" s="312" t="n"/>
+      <c r="F13" s="377" t="n"/>
+      <c r="H13" s="378" t="n"/>
+      <c r="I13" s="312" t="n"/>
+      <c r="J13" s="312" t="n"/>
+      <c r="K13" s="312" t="n"/>
+      <c r="L13" s="379" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="74">
+      <c r="B14" s="388" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -44969,7 +45739,7 @@
       <c r="D14" s="286" t="n"/>
       <c r="E14" s="286" t="n"/>
       <c r="F14" s="287" t="n"/>
-      <c r="H14" s="241" t="inlineStr">
+      <c r="H14" s="389" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -44979,7 +45749,7 @@
       <c r="K14" s="288" t="n"/>
       <c r="L14" s="289" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1" s="74">
       <c r="B15" s="290" t="n"/>
       <c r="C15" s="291" t="n"/>
       <c r="D15" s="291" t="n"/>
@@ -44991,70 +45761,185 @@
       <c r="K15" s="294" t="n"/>
       <c r="L15" s="295" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="85" t="inlineStr">
+    <row r="16" ht="10" customHeight="1" s="74"/>
+    <row r="17" ht="26" customHeight="1" s="74">
+      <c r="B17" s="390" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="198" t="inlineStr">
+      <c r="C17" s="303" t="n"/>
+      <c r="D17" s="303" t="n"/>
+      <c r="E17" s="303" t="n"/>
+      <c r="F17" s="303" t="n"/>
+      <c r="G17" s="303" t="n"/>
+      <c r="H17" s="303" t="n"/>
+      <c r="I17" s="303" t="n"/>
+      <c r="J17" s="303" t="n"/>
+      <c r="K17" s="303" t="n"/>
+      <c r="L17" s="354" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="74">
+      <c r="B18" s="391" t="n"/>
+      <c r="C18" s="312" t="n"/>
+      <c r="D18" s="312" t="n"/>
+      <c r="E18" s="312" t="n"/>
+      <c r="F18" s="312" t="n"/>
+      <c r="G18" s="312" t="n"/>
+      <c r="H18" s="312" t="n"/>
+      <c r="I18" s="312" t="n"/>
+      <c r="J18" s="312" t="n"/>
+      <c r="K18" s="312" t="n"/>
+      <c r="L18" s="313" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="74">
+      <c r="B19" s="392" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="242" t="inlineStr">
+      <c r="C19" s="312" t="n"/>
+      <c r="D19" s="312" t="n"/>
+      <c r="E19" s="312" t="n"/>
+      <c r="F19" s="312" t="n"/>
+      <c r="G19" s="312" t="n"/>
+      <c r="H19" s="312" t="n"/>
+      <c r="I19" s="312" t="n"/>
+      <c r="J19" s="312" t="n"/>
+      <c r="K19" s="312" t="n"/>
+      <c r="L19" s="313" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="74">
+      <c r="B20" s="393" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="198" t="inlineStr">
+      <c r="C20" s="312" t="n"/>
+      <c r="D20" s="312" t="n"/>
+      <c r="E20" s="312" t="n"/>
+      <c r="F20" s="312" t="n"/>
+      <c r="G20" s="312" t="n"/>
+      <c r="H20" s="312" t="n"/>
+      <c r="I20" s="312" t="n"/>
+      <c r="J20" s="312" t="n"/>
+      <c r="K20" s="312" t="n"/>
+      <c r="L20" s="313" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="74">
+      <c r="B21" s="392" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="242" t="inlineStr">
+      <c r="C21" s="312" t="n"/>
+      <c r="D21" s="312" t="n"/>
+      <c r="E21" s="312" t="n"/>
+      <c r="F21" s="312" t="n"/>
+      <c r="G21" s="312" t="n"/>
+      <c r="H21" s="312" t="n"/>
+      <c r="I21" s="312" t="n"/>
+      <c r="J21" s="312" t="n"/>
+      <c r="K21" s="312" t="n"/>
+      <c r="L21" s="313" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="74">
+      <c r="B22" s="393" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="198" t="inlineStr">
+      <c r="C22" s="312" t="n"/>
+      <c r="D22" s="312" t="n"/>
+      <c r="E22" s="312" t="n"/>
+      <c r="F22" s="312" t="n"/>
+      <c r="G22" s="312" t="n"/>
+      <c r="H22" s="312" t="n"/>
+      <c r="I22" s="312" t="n"/>
+      <c r="J22" s="312" t="n"/>
+      <c r="K22" s="312" t="n"/>
+      <c r="L22" s="313" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="74">
+      <c r="B23" s="392" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="242" t="inlineStr">
+      <c r="C23" s="312" t="n"/>
+      <c r="D23" s="312" t="n"/>
+      <c r="E23" s="312" t="n"/>
+      <c r="F23" s="312" t="n"/>
+      <c r="G23" s="312" t="n"/>
+      <c r="H23" s="312" t="n"/>
+      <c r="I23" s="312" t="n"/>
+      <c r="J23" s="312" t="n"/>
+      <c r="K23" s="312" t="n"/>
+      <c r="L23" s="313" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="74">
+      <c r="B24" s="393" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="198" t="inlineStr">
+      <c r="C24" s="312" t="n"/>
+      <c r="D24" s="312" t="n"/>
+      <c r="E24" s="312" t="n"/>
+      <c r="F24" s="312" t="n"/>
+      <c r="G24" s="312" t="n"/>
+      <c r="H24" s="312" t="n"/>
+      <c r="I24" s="312" t="n"/>
+      <c r="J24" s="312" t="n"/>
+      <c r="K24" s="312" t="n"/>
+      <c r="L24" s="313" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="74">
+      <c r="B25" s="392" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="242" t="inlineStr">
+      <c r="C25" s="312" t="n"/>
+      <c r="D25" s="312" t="n"/>
+      <c r="E25" s="312" t="n"/>
+      <c r="F25" s="312" t="n"/>
+      <c r="G25" s="312" t="n"/>
+      <c r="H25" s="312" t="n"/>
+      <c r="I25" s="312" t="n"/>
+      <c r="J25" s="312" t="n"/>
+      <c r="K25" s="312" t="n"/>
+      <c r="L25" s="313" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="74">
+      <c r="B26" s="393" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="312" t="n"/>
+      <c r="D26" s="312" t="n"/>
+      <c r="E26" s="312" t="n"/>
+      <c r="F26" s="312" t="n"/>
+      <c r="G26" s="312" t="n"/>
+      <c r="H26" s="312" t="n"/>
+      <c r="I26" s="312" t="n"/>
+      <c r="J26" s="312" t="n"/>
+      <c r="K26" s="312" t="n"/>
+      <c r="L26" s="313" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="74">
+      <c r="B27" s="371" t="n"/>
+      <c r="C27" s="322" t="n"/>
+      <c r="D27" s="322" t="n"/>
+      <c r="E27" s="322" t="n"/>
+      <c r="F27" s="322" t="n"/>
+      <c r="G27" s="322" t="n"/>
+      <c r="H27" s="322" t="n"/>
+      <c r="I27" s="322" t="n"/>
+      <c r="J27" s="322" t="n"/>
+      <c r="K27" s="322" t="n"/>
+      <c r="L27" s="323" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -45096,7 +45981,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="249" t="inlineStr">
         <is>
@@ -45591,7 +46475,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="252" t="inlineStr">
         <is>
@@ -46338,7 +47221,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="257" t="inlineStr">
         <is>
@@ -47016,7 +47898,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="261" t="inlineStr">
         <is>
@@ -47566,7 +48447,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="74">
       <c r="A3" s="264" t="inlineStr">
         <is>
